--- a/Button tables.xlsx
+++ b/Button tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\cockpit_arduino\cockpit_joystick\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\cockpit_arduino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2800FEED-7FD0-4079-BA5A-42FE48F57CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58493AB-5991-4EBB-BF6C-078A1D3566E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="3336" windowWidth="30420" windowHeight="18336" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
+    <workbookView xWindow="60450" yWindow="12945" windowWidth="30420" windowHeight="18330" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Radio Arduino" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="119">
   <si>
     <t>Key</t>
   </si>
@@ -376,6 +376,24 @@
   </si>
   <si>
     <t>Vi gör en översättningstabell från signaler till knappar. I denna reserverar vi plats för knappar som definieras av kombinationer av signaler. Efter översättningen gör vi en manuell kod som löser dessa kombinationer.</t>
+  </si>
+  <si>
+    <t>Left Rotary CW</t>
+  </si>
+  <si>
+    <t>Left Rotary CCW</t>
+  </si>
+  <si>
+    <t>Right Rotary CW</t>
+  </si>
+  <si>
+    <t>Right Rotary CCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLR </t>
+  </si>
+  <si>
+    <t>ENT</t>
   </si>
 </sst>
 </file>
@@ -441,7 +459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -778,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D25623C-CB7E-43B5-9444-FC757D6B6CE6}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -867,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F24" si="1">F3+1</f>
+        <f t="shared" ref="F4:F17" si="1">F3+1</f>
         <v>2</v>
       </c>
     </row>
@@ -1114,7 +1132,7 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1124,13 +1142,17 @@
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1140,6 +1162,10 @@
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ref="F18:F29" si="2">F17+1</f>
         <v>16</v>
       </c>
     </row>
@@ -1159,8 +1185,8 @@
         <v>17</v>
       </c>
       <c r="F19">
-        <f>F16+1</f>
-        <v>15</v>
+        <f t="shared" si="2"/>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1179,8 +1205,8 @@
         <v>18</v>
       </c>
       <c r="F20">
-        <f>F19+1</f>
-        <v>16</v>
+        <f t="shared" si="2"/>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1199,8 +1225,8 @@
         <v>19</v>
       </c>
       <c r="F21">
-        <f>F20+1</f>
-        <v>17</v>
+        <f t="shared" si="2"/>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1219,8 +1245,8 @@
         <v>20</v>
       </c>
       <c r="F22">
-        <f>F21+1</f>
-        <v>18</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1239,8 +1265,8 @@
         <v>21</v>
       </c>
       <c r="F23">
-        <f>F22+1</f>
-        <v>19</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1259,8 +1285,8 @@
         <v>22</v>
       </c>
       <c r="F24">
-        <f>F23+1</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1279,8 +1305,8 @@
         <v>23</v>
       </c>
       <c r="F25">
-        <f>F24+1</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1299,8 +1325,8 @@
         <v>24</v>
       </c>
       <c r="F26">
-        <f>F25+1</f>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1319,8 +1345,8 @@
         <v>25</v>
       </c>
       <c r="F27">
-        <f>F26+1</f>
-        <v>23</v>
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1339,8 +1365,8 @@
         <v>26</v>
       </c>
       <c r="F28">
-        <f>F27+1</f>
-        <v>24</v>
+        <f t="shared" si="2"/>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1359,8 +1385,8 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <f>F28+1</f>
-        <v>25</v>
+        <f t="shared" si="2"/>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1431,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="E34">
-        <f t="shared" ref="E34:E60" si="2">E33+1</f>
+        <f t="shared" ref="E34:E60" si="3">E33+1</f>
         <v>2</v>
       </c>
     </row>
@@ -1444,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -1457,7 +1483,7 @@
         <v>10</v>
       </c>
       <c r="E36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -1470,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="E37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -1483,7 +1509,7 @@
         <v>40</v>
       </c>
       <c r="E38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -1496,7 +1522,7 @@
         <v>80</v>
       </c>
       <c r="E39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -1509,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -1522,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="E41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
@@ -1538,11 +1564,11 @@
         <v>4</v>
       </c>
       <c r="E42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G42" t="s">
         <v>108</v>
@@ -1560,12 +1586,12 @@
         <v>8</v>
       </c>
       <c r="E43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="F43">
         <f>F42+1</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -1577,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="E44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
@@ -1593,12 +1619,12 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="F45">
         <f>F43+1</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1613,12 +1639,12 @@
         <v>40</v>
       </c>
       <c r="E46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="F46">
         <f>F45+1</f>
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1633,12 +1659,12 @@
         <v>80</v>
       </c>
       <c r="E47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="F47">
         <f>F46+1</f>
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -1653,12 +1679,12 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="F48">
         <f>F47+1</f>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1673,12 +1699,12 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="F49">
         <f>F48+1</f>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1693,12 +1719,12 @@
         <v>4</v>
       </c>
       <c r="E50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="F50">
         <f>F49+1</f>
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1710,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="E51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -1723,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="E52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
@@ -1736,7 +1762,7 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
     </row>
@@ -1749,7 +1775,7 @@
         <v>40</v>
       </c>
       <c r="E54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
@@ -1765,7 +1791,7 @@
         <v>80</v>
       </c>
       <c r="E55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
     </row>
@@ -1781,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
     </row>
@@ -1797,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
@@ -1813,7 +1839,7 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
     </row>
@@ -1829,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="E59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
     </row>
@@ -1845,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="E60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
@@ -1882,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -1902,7 +1928,7 @@
       </c>
       <c r="F63">
         <f>F62+1</f>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -1914,7 +1940,7 @@
         <v>4</v>
       </c>
       <c r="E64">
-        <f t="shared" ref="E64:E90" si="3">E63+1</f>
+        <f t="shared" ref="E64:E90" si="4">E63+1</f>
         <v>2</v>
       </c>
     </row>
@@ -1927,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="E65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -1940,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="E66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
     </row>
@@ -1956,12 +1982,12 @@
         <v>20</v>
       </c>
       <c r="E67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="F67">
         <f>F63+1</f>
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1976,12 +2002,12 @@
         <v>40</v>
       </c>
       <c r="E68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="F68">
         <f>F67+1</f>
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1996,15 +2022,15 @@
         <v>80</v>
       </c>
       <c r="E69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="F69">
         <f>F68+1</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G69">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H69" t="s">
         <v>110</v>
@@ -2019,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
     </row>
@@ -2032,7 +2058,7 @@
         <v>2</v>
       </c>
       <c r="E71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
     </row>
@@ -2048,11 +2074,11 @@
         <v>4</v>
       </c>
       <c r="E72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F72">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -2067,15 +2093,15 @@
         <v>8</v>
       </c>
       <c r="E73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="F73">
         <f>F72+1</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G73">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H73" t="s">
         <v>111</v>
@@ -2093,11 +2119,11 @@
         <v>10</v>
       </c>
       <c r="E74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="F74">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -2112,12 +2138,12 @@
         <v>20</v>
       </c>
       <c r="E75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="F75">
         <f>F74+1</f>
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
@@ -2129,7 +2155,7 @@
         <v>40</v>
       </c>
       <c r="E76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
     </row>
@@ -2145,12 +2171,12 @@
         <v>80</v>
       </c>
       <c r="E77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="F77">
         <f>F75+1</f>
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -2165,12 +2191,12 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="F78">
-        <f>F77+1</f>
-        <v>46</v>
+        <f t="shared" ref="F78:F86" si="5">F77+1</f>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
@@ -2185,12 +2211,12 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="F79">
-        <f>F78+1</f>
-        <v>47</v>
+        <f t="shared" si="5"/>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
@@ -2205,12 +2231,12 @@
         <v>4</v>
       </c>
       <c r="E80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="F80">
-        <f>F79+1</f>
-        <v>48</v>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2225,12 +2251,12 @@
         <v>8</v>
       </c>
       <c r="E81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="F81">
-        <f>F80+1</f>
-        <v>49</v>
+        <f t="shared" si="5"/>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2245,12 +2271,12 @@
         <v>10</v>
       </c>
       <c r="E82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="F82">
-        <f>F81+1</f>
-        <v>50</v>
+        <f t="shared" si="5"/>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2265,12 +2291,12 @@
         <v>20</v>
       </c>
       <c r="E83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="F83">
-        <f>F82+1</f>
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2285,12 +2311,12 @@
         <v>40</v>
       </c>
       <c r="E84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="F84">
-        <f>F83+1</f>
-        <v>52</v>
+        <f t="shared" si="5"/>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2305,12 +2331,12 @@
         <v>80</v>
       </c>
       <c r="E85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="F85">
-        <f>F84+1</f>
-        <v>53</v>
+        <f t="shared" si="5"/>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -2325,12 +2351,12 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="F86">
-        <f>F85+1</f>
-        <v>54</v>
+        <f t="shared" si="5"/>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2345,7 +2371,7 @@
         <v>2</v>
       </c>
       <c r="E87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
     </row>
@@ -2361,7 +2387,7 @@
         <v>4</v>
       </c>
       <c r="E88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
     </row>
@@ -2377,7 +2403,7 @@
         <v>8</v>
       </c>
       <c r="E89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
     </row>
@@ -2393,7 +2419,7 @@
         <v>10</v>
       </c>
       <c r="E90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
     </row>
@@ -2413,122 +2439,161 @@
         <v>29</v>
       </c>
     </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" t="s">
+        <v>113</v>
+      </c>
+      <c r="F92">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="4"/>
+      <c r="B93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93">
+        <v>58</v>
+      </c>
+    </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="4"/>
+      <c r="B94" t="s">
+        <v>115</v>
+      </c>
+      <c r="F94">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="4"/>
+      <c r="B95" t="s">
+        <v>116</v>
+      </c>
+      <c r="F95">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>68</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B97" t="s">
         <v>69</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
         <v>79</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>70</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B99" t="s">
         <v>78</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
         <v>80</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>71</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B101" t="s">
         <v>81</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
         <v>82</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="5" t="s">
+    <row r="112" spans="1:12" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="5"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:A31"/>
     <mergeCell ref="A32:A61"/>
     <mergeCell ref="A62:A91"/>
-    <mergeCell ref="A109:L109"/>
+    <mergeCell ref="A112:L112"/>
+    <mergeCell ref="A92:A95"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Button tables.xlsx
+++ b/Button tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\cockpit_arduino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58493AB-5991-4EBB-BF6C-078A1D3566E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E558506-15F2-4FBC-BA01-BBD2D955D7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60450" yWindow="12945" windowWidth="30420" windowHeight="18330" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
+    <workbookView xWindow="1020" yWindow="4140" windowWidth="15636" windowHeight="18336" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Radio Arduino" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="122">
   <si>
     <t>Key</t>
   </si>
@@ -117,12 +117,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>DDI Left = ?</t>
-  </si>
-  <si>
-    <t>DDI Right = ?</t>
-  </si>
-  <si>
     <t>Radio = 0</t>
   </si>
   <si>
@@ -333,12 +327,6 @@
     <t>ADF Up</t>
   </si>
   <si>
-    <t>HDG Switch On</t>
-  </si>
-  <si>
-    <t>CRS Switch On</t>
-  </si>
-  <si>
     <t>Func sel 1 A/P</t>
   </si>
   <si>
@@ -394,6 +382,27 @@
   </si>
   <si>
     <t>ENT</t>
+  </si>
+  <si>
+    <t>DDI Left = 2</t>
+  </si>
+  <si>
+    <t>DDI Bottom = 1</t>
+  </si>
+  <si>
+    <t>DDI Right = 0</t>
+  </si>
+  <si>
+    <t>CRS Switch Left</t>
+  </si>
+  <si>
+    <t>HDG Switch Right</t>
+  </si>
+  <si>
+    <t>HDG Switch Left</t>
+  </si>
+  <si>
+    <t>CRS Switch Right</t>
   </si>
 </sst>
 </file>
@@ -814,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -826,15 +835,15 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -852,7 +861,7 @@
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -872,7 +881,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -892,7 +901,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -912,7 +921,7 @@
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -932,7 +941,7 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -952,7 +961,7 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -972,7 +981,7 @@
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -992,7 +1001,7 @@
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1012,7 +1021,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1032,7 +1041,7 @@
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1052,7 +1061,7 @@
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1072,7 +1081,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>7</v>
@@ -1092,7 +1101,7 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1112,7 +1121,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -1132,7 +1141,7 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1152,7 +1161,7 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1172,7 +1181,7 @@
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -1192,7 +1201,7 @@
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -1212,7 +1221,7 @@
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -1232,7 +1241,7 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -1252,7 +1261,7 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -1272,7 +1281,7 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -1292,7 +1301,7 @@
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -1312,7 +1321,7 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1332,7 +1341,7 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -1352,7 +1361,7 @@
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -1372,7 +1381,7 @@
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1423,7 +1432,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C32">
         <v>19</v>
@@ -1555,7 +1564,7 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C42">
         <v>18</v>
@@ -1571,13 +1580,13 @@
         <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C43">
         <v>18</v>
@@ -1610,7 +1619,7 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C45">
         <v>18</v>
@@ -1630,7 +1639,7 @@
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C46">
         <v>18</v>
@@ -1649,9 +1658,6 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
       <c r="C47">
         <v>18</v>
       </c>
@@ -1661,16 +1667,12 @@
       <c r="E47">
         <f t="shared" si="3"/>
         <v>15</v>
-      </c>
-      <c r="F47">
-        <f>F46+1</f>
-        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C48">
         <v>17</v>
@@ -1683,14 +1685,14 @@
         <v>16</v>
       </c>
       <c r="F48">
-        <f>F47+1</f>
-        <v>33</v>
+        <f>F46+1</f>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C49">
         <v>17</v>
@@ -1704,13 +1706,13 @@
       </c>
       <c r="F49">
         <f>F48+1</f>
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C50">
         <v>17</v>
@@ -1724,11 +1726,14 @@
       </c>
       <c r="F50">
         <f>F49+1</f>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
       <c r="C51">
         <v>17</v>
       </c>
@@ -1738,6 +1743,10 @@
       <c r="E51">
         <f t="shared" si="3"/>
         <v>19</v>
+      </c>
+      <c r="F51">
+        <f>F50+1</f>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -1893,10 +1902,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C62">
         <v>30</v>
@@ -1914,7 +1923,7 @@
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C63">
         <v>30</v>
@@ -1933,6 +1942,9 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
+      <c r="B64" t="s">
+        <v>121</v>
+      </c>
       <c r="C64">
         <v>30</v>
       </c>
@@ -1943,9 +1955,15 @@
         <f t="shared" ref="E64:E90" si="4">E63+1</f>
         <v>2</v>
       </c>
+      <c r="F64">
+        <v>57</v>
+      </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
+      <c r="B65" t="s">
+        <v>118</v>
+      </c>
       <c r="C65">
         <v>30</v>
       </c>
@@ -1955,6 +1973,9 @@
       <c r="E65">
         <f t="shared" si="4"/>
         <v>3</v>
+      </c>
+      <c r="F65">
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -1973,7 +1994,7 @@
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C67">
         <v>30</v>
@@ -1993,7 +2014,7 @@
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C68">
         <v>30</v>
@@ -2013,7 +2034,7 @@
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C69">
         <v>30</v>
@@ -2033,7 +2054,7 @@
         <v>41</v>
       </c>
       <c r="H69" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -2065,7 +2086,7 @@
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C72">
         <v>29</v>
@@ -2084,7 +2105,7 @@
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C73">
         <v>29</v>
@@ -2104,13 +2125,13 @@
         <v>44</v>
       </c>
       <c r="H73" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C74">
         <v>29</v>
@@ -2129,7 +2150,7 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C75">
         <v>29</v>
@@ -2162,7 +2183,7 @@
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C77">
         <v>29</v>
@@ -2182,7 +2203,7 @@
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C78">
         <v>28</v>
@@ -2202,7 +2223,7 @@
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C79">
         <v>28</v>
@@ -2222,7 +2243,7 @@
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C80">
         <v>28</v>
@@ -2242,7 +2263,7 @@
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C81">
         <v>28</v>
@@ -2262,7 +2283,7 @@
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C82">
         <v>28</v>
@@ -2282,7 +2303,7 @@
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C83">
         <v>28</v>
@@ -2302,7 +2323,7 @@
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C84">
         <v>28</v>
@@ -2322,7 +2343,7 @@
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C85">
         <v>28</v>
@@ -2342,7 +2363,7 @@
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C86">
         <v>27</v>
@@ -2441,139 +2462,139 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F92">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F93">
-        <v>58</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F94">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F95">
-        <v>60</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -2602,16 +2623,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AF7111-1B37-497D-B08D-3EB3AFC0EDCF}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="3" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2619,1187 +2641,1767 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <f>C2+1</f>
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f>E2+1</f>
         <v>1</v>
       </c>
-      <c r="D3">
-        <f>D2+1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <f>F2+1</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C30" si="0">C3+1</f>
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E30" si="0">E3+1</f>
         <v>2</v>
       </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D24" si="1">D3+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <f t="shared" ref="F4:F24" si="1">F3+1</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>80</v>
+      </c>
+      <c r="E9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
         <v>18</v>
       </c>
       <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>40</v>
+      </c>
+      <c r="E16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>80</v>
+      </c>
+      <c r="E17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
         <v>20</v>
       </c>
       <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
         <v>21</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
         <v>23</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>20</v>
+      </c>
+      <c r="E23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>40</v>
+      </c>
+      <c r="E24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
         <v>25</v>
       </c>
       <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>80</v>
+      </c>
+      <c r="E25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
         <v>25</v>
       </c>
       <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
         <v>25</v>
       </c>
       <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
         <v>25</v>
       </c>
       <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
         <v>25</v>
       </c>
       <c r="C31">
-        <f>C30+1</f>
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31">
+        <f>E30+1</f>
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32">
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
         <v>0</v>
       </c>
-      <c r="D32">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" t="s">
         <v>5</v>
       </c>
       <c r="C33">
-        <f>C32+1</f>
+        <v>19</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <f>E32+1</f>
         <v>1</v>
       </c>
-      <c r="D33">
-        <f>D32+1</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <f>F32+1</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
-        <f t="shared" ref="C34:C60" si="2">C33+1</f>
+        <v>19</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ref="E34:E60" si="2">E33+1</f>
         <v>2</v>
       </c>
-      <c r="D34">
-        <f t="shared" ref="D34:D54" si="3">D33+1</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <f t="shared" ref="F34:F54" si="3">F33+1</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" t="s">
         <v>7</v>
       </c>
       <c r="C35">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D35">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" t="s">
         <v>8</v>
       </c>
       <c r="C36">
+        <v>19</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D36">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37">
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D37">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>40</v>
+      </c>
+      <c r="E38">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D38">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>80</v>
+      </c>
+      <c r="E39">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D39">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40">
+        <v>18</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="D40">
-        <f t="shared" si="3"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41">
+        <v>18</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="D41">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <f t="shared" si="3"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" t="s">
         <v>14</v>
       </c>
       <c r="C42">
+        <v>18</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="D42">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" t="s">
         <v>15</v>
       </c>
       <c r="C43">
+        <v>18</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="D43">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" t="s">
         <v>16</v>
       </c>
       <c r="C44">
+        <v>18</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D44">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <f t="shared" si="3"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
         <v>17</v>
       </c>
       <c r="C45">
+        <v>18</v>
+      </c>
+      <c r="D45">
+        <v>20</v>
+      </c>
+      <c r="E45">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="D45">
-        <f t="shared" si="3"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <f t="shared" si="3"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" t="s">
         <v>18</v>
       </c>
       <c r="C46">
+        <v>18</v>
+      </c>
+      <c r="D46">
+        <v>40</v>
+      </c>
+      <c r="E46">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="D46">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47">
+        <v>18</v>
+      </c>
+      <c r="D47">
+        <v>80</v>
+      </c>
+      <c r="E47">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="D47">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F47">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
         <v>20</v>
       </c>
       <c r="C48">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="D48">
-        <f t="shared" si="3"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F48">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
         <v>21</v>
       </c>
       <c r="C49">
+        <v>17</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="D49">
-        <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F49">
+        <f t="shared" si="3"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
         <v>22</v>
       </c>
       <c r="C50">
+        <v>17</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="D50">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" t="s">
         <v>23</v>
       </c>
       <c r="C51">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="D51">
-        <f t="shared" si="3"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F51">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" t="s">
         <v>24</v>
       </c>
       <c r="C52">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="D52">
-        <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F52">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" t="s">
         <v>24</v>
       </c>
       <c r="C53">
+        <v>17</v>
+      </c>
+      <c r="D53">
+        <v>20</v>
+      </c>
+      <c r="E53">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="D53">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F53">
+        <f t="shared" si="3"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" t="s">
         <v>24</v>
       </c>
       <c r="C54">
+        <v>17</v>
+      </c>
+      <c r="D54">
+        <v>40</v>
+      </c>
+      <c r="E54">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="D54">
-        <f t="shared" si="3"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F54">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
         <v>25</v>
       </c>
       <c r="C55">
+        <v>17</v>
+      </c>
+      <c r="D55">
+        <v>80</v>
+      </c>
+      <c r="E55">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
         <v>25</v>
       </c>
       <c r="C56">
+        <v>16</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
         <v>25</v>
       </c>
       <c r="C57">
+        <v>16</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
         <v>25</v>
       </c>
       <c r="C58">
+        <v>16</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
         <v>25</v>
       </c>
       <c r="C59">
+        <v>16</v>
+      </c>
+      <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
         <v>25</v>
       </c>
       <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" t="s">
         <v>25</v>
       </c>
       <c r="C61">
-        <f>C60+1</f>
+        <v>16</v>
+      </c>
+      <c r="D61">
+        <v>20</v>
+      </c>
+      <c r="E61">
+        <f>E60+1</f>
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
       </c>
       <c r="C62">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
         <v>0</v>
       </c>
-      <c r="D62">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" t="s">
         <v>5</v>
       </c>
       <c r="C63">
-        <f>C62+1</f>
+        <v>30</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <f>E62+1</f>
         <v>1</v>
       </c>
-      <c r="D63">
-        <f>D62+1</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F63">
+        <f>F62+1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" t="s">
         <v>6</v>
       </c>
       <c r="C64">
-        <f t="shared" ref="C64:C90" si="4">C63+1</f>
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <f t="shared" ref="E64:E90" si="4">E63+1</f>
         <v>2</v>
       </c>
-      <c r="D64">
-        <f t="shared" ref="D64:D84" si="5">D63+1</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F64">
+        <f t="shared" ref="F64:F84" si="5">F63+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" t="s">
         <v>7</v>
       </c>
       <c r="C65">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>8</v>
+      </c>
+      <c r="E65">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="D65">
+      <c r="F65">
         <f t="shared" si="5"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" t="s">
         <v>8</v>
       </c>
       <c r="C66">
+        <v>30</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="D66">
+      <c r="F66">
         <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C67">
+        <v>30</v>
+      </c>
+      <c r="D67">
+        <v>20</v>
+      </c>
+      <c r="E67">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="D67">
+      <c r="F67">
         <f t="shared" si="5"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C68">
+        <v>30</v>
+      </c>
+      <c r="D68">
+        <v>40</v>
+      </c>
+      <c r="E68">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="D68">
+      <c r="F68">
         <f t="shared" si="5"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C69">
+        <v>30</v>
+      </c>
+      <c r="D69">
+        <v>80</v>
+      </c>
+      <c r="E69">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="D69">
+      <c r="F69">
         <f t="shared" si="5"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C70">
-        <f t="shared" si="4"/>
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="F70">
         <f t="shared" si="5"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C71">
+        <v>29</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="D71">
+      <c r="F71">
         <f t="shared" si="5"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C72">
+        <v>29</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="D72">
+      <c r="F72">
         <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C73">
+        <v>29</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="D73">
+      <c r="F73">
         <f t="shared" si="5"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" t="s">
         <v>16</v>
       </c>
       <c r="C74">
+        <v>29</v>
+      </c>
+      <c r="D74">
+        <v>10</v>
+      </c>
+      <c r="E74">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="D74">
+      <c r="F74">
         <f t="shared" si="5"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C75">
+        <v>29</v>
+      </c>
+      <c r="D75">
+        <v>20</v>
+      </c>
+      <c r="E75">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="D75">
+      <c r="F75">
         <f t="shared" si="5"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C76">
+        <v>29</v>
+      </c>
+      <c r="D76">
+        <v>40</v>
+      </c>
+      <c r="E76">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="D76">
+      <c r="F76">
         <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C77">
+        <v>29</v>
+      </c>
+      <c r="D77">
+        <v>80</v>
+      </c>
+      <c r="E77">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="D77">
+      <c r="F77">
         <f t="shared" si="5"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C78">
+        <v>28</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="D78">
+      <c r="F78">
         <f t="shared" si="5"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C79">
+        <v>28</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="D79">
+      <c r="F79">
         <f t="shared" si="5"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C80">
+        <v>28</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="D80">
+      <c r="F80">
         <f t="shared" si="5"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C81">
+        <v>28</v>
+      </c>
+      <c r="D81">
+        <v>8</v>
+      </c>
+      <c r="E81">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="D81">
+      <c r="F81">
         <f t="shared" si="5"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" t="s">
         <v>24</v>
       </c>
       <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="D82">
+      <c r="F82">
         <f t="shared" si="5"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" t="s">
         <v>24</v>
       </c>
       <c r="C83">
+        <v>28</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+      <c r="E83">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="D83">
+      <c r="F83">
         <f t="shared" si="5"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" t="s">
         <v>24</v>
       </c>
       <c r="C84">
+        <v>28</v>
+      </c>
+      <c r="D84">
+        <v>40</v>
+      </c>
+      <c r="E84">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="D84">
+      <c r="F84">
         <f t="shared" si="5"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" t="s">
         <v>25</v>
       </c>
       <c r="C85">
+        <v>28</v>
+      </c>
+      <c r="D85">
+        <v>80</v>
+      </c>
+      <c r="E85">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" t="s">
         <v>25</v>
       </c>
       <c r="C86">
+        <v>27</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" t="s">
         <v>25</v>
       </c>
       <c r="C87">
+        <v>27</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" t="s">
         <v>25</v>
       </c>
       <c r="C88">
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" t="s">
         <v>25</v>
       </c>
       <c r="C89">
-        <f t="shared" si="4"/>
         <v>27</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D89">
+        <v>8</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" t="s">
         <v>25</v>
       </c>
       <c r="C90">
+        <v>27</v>
+      </c>
+      <c r="D90">
+        <v>10</v>
+      </c>
+      <c r="E90">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" t="s">
         <v>25</v>
       </c>
       <c r="C91">
-        <f>C90+1</f>
+        <v>27</v>
+      </c>
+      <c r="D91">
+        <v>20</v>
+      </c>
+      <c r="E91">
+        <f>E90+1</f>
         <v>29</v>
       </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C97" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C98" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C99" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C100" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C101" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C102" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Button tables.xlsx
+++ b/Button tables.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\cockpit_arduino\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_dummy\cockpit_arduino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E558506-15F2-4FBC-BA01-BBD2D955D7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329F8919-327C-4F26-B956-38E8D61C7794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="4140" windowWidth="15636" windowHeight="18336" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
+    <workbookView xWindow="26025" yWindow="1965" windowWidth="31845" windowHeight="16410" activeTab="1" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Radio Arduino" sheetId="2" r:id="rId1"/>
-    <sheet name="DDI Arduino" sheetId="1" r:id="rId2"/>
+    <sheet name=" Engine Arduino" sheetId="3" r:id="rId1"/>
+    <sheet name="Radio Arduino" sheetId="2" r:id="rId2"/>
+    <sheet name="DDI Arduino" sheetId="1" r:id="rId3"/>
+    <sheet name="PIC data formating" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="194">
   <si>
     <t>Key</t>
   </si>
@@ -403,13 +405,229 @@
   </si>
   <si>
     <t>CRS Switch Right</t>
+  </si>
+  <si>
+    <t>PIC Input</t>
+  </si>
+  <si>
+    <t>R_ADC0</t>
+  </si>
+  <si>
+    <t>R_ADC1</t>
+  </si>
+  <si>
+    <t>G_ADC0</t>
+  </si>
+  <si>
+    <t>G_ADC1</t>
+  </si>
+  <si>
+    <t>L FUS MSL</t>
+  </si>
+  <si>
+    <t>SAFE</t>
+  </si>
+  <si>
+    <t>R FUS MSL</t>
+  </si>
+  <si>
+    <t>Rack LCHR</t>
+  </si>
+  <si>
+    <t>Stores</t>
+  </si>
+  <si>
+    <t>Launch bar Extract</t>
+  </si>
+  <si>
+    <t>Flap Full</t>
+  </si>
+  <si>
+    <t>Flap Auto</t>
+  </si>
+  <si>
+    <t>Taxi Light On</t>
+  </si>
+  <si>
+    <t>Anti Skid On</t>
+  </si>
+  <si>
+    <t>Hook Bypass Field</t>
+  </si>
+  <si>
+    <t>Not Connected</t>
+  </si>
+  <si>
+    <t>Engine 1</t>
+  </si>
+  <si>
+    <t>Engine 2</t>
+  </si>
+  <si>
+    <t>Engine 3</t>
+  </si>
+  <si>
+    <t>Engine 4</t>
+  </si>
+  <si>
+    <t>Engine 5</t>
+  </si>
+  <si>
+    <t>Engine 6</t>
+  </si>
+  <si>
+    <t>Jettison 1</t>
+  </si>
+  <si>
+    <t>Jettison 2</t>
+  </si>
+  <si>
+    <t>Jettison 3</t>
+  </si>
+  <si>
+    <t>Jettison 4</t>
+  </si>
+  <si>
+    <t>Jettison 5</t>
+  </si>
+  <si>
+    <t>HUD Symbol Rej 1</t>
+  </si>
+  <si>
+    <t>HUD Symbol Rej 2</t>
+  </si>
+  <si>
+    <t>HUD Symbol Day</t>
+  </si>
+  <si>
+    <t>Alt Switch Baro</t>
+  </si>
+  <si>
+    <t>HUD Video Control W/B</t>
+  </si>
+  <si>
+    <t>HUD Video Control Off</t>
+  </si>
+  <si>
+    <t>Attitude Source INS</t>
+  </si>
+  <si>
+    <t>Attitude Source Stdby</t>
+  </si>
+  <si>
+    <t>HUD Symbology Brightnes</t>
+  </si>
+  <si>
+    <t>AoA Indexer Brightness</t>
+  </si>
+  <si>
+    <t>HUD Balance</t>
+  </si>
+  <si>
+    <t>Landing Gear</t>
+  </si>
+  <si>
+    <t>Jettison Button</t>
+  </si>
+  <si>
+    <t>Rotary diff 1</t>
+  </si>
+  <si>
+    <t>ADC 0</t>
+  </si>
+  <si>
+    <t>Rotary diff 0</t>
+  </si>
+  <si>
+    <t>ADC 1</t>
+  </si>
+  <si>
+    <t>Top Row</t>
+  </si>
+  <si>
+    <t>Left Column</t>
+  </si>
+  <si>
+    <t>Bottom Row</t>
+  </si>
+  <si>
+    <t>Right Column</t>
+  </si>
+  <si>
+    <t>Rotary</t>
+  </si>
+  <si>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>R_B_n</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>Pin</t>
+  </si>
+  <si>
+    <t>H42</t>
+  </si>
+  <si>
+    <t>3;4</t>
+  </si>
+  <si>
+    <t>1;2</t>
+  </si>
+  <si>
+    <t>H43</t>
+  </si>
+  <si>
+    <t>9;10</t>
+  </si>
+  <si>
+    <t>5;6</t>
+  </si>
+  <si>
+    <t>7;8</t>
+  </si>
+  <si>
+    <t>H44</t>
+  </si>
+  <si>
+    <t>H40</t>
+  </si>
+  <si>
+    <t>H35</t>
+  </si>
+  <si>
+    <t>H33</t>
+  </si>
+  <si>
+    <t>H32</t>
+  </si>
+  <si>
+    <t>H34</t>
+  </si>
+  <si>
+    <t>H38</t>
+  </si>
+  <si>
+    <t>H41</t>
+  </si>
+  <si>
+    <t>H45</t>
+  </si>
+  <si>
+    <t>H10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,16 +657,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -456,11 +692,166 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -471,8 +862,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Dålig" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -804,18 +1238,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D25623C-CB7E-43B5-9444-FC757D6B6CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF364BB8-A1D7-4889-9DA3-577BF721609C}">
   <dimension ref="A1:L112"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -838,12 +1272,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -858,10 +1292,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -874,14 +1308,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <f>F2+1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -890,18 +1323,17 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E30" si="0">E3+1</f>
+        <f t="shared" ref="E4:E19" si="0">E3+1</f>
         <v>2</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F17" si="1">F3+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -914,14 +1346,13 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -934,14 +1365,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -954,14 +1384,13 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -973,15 +1402,11 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F8">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -993,15 +1418,11 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1013,15 +1434,11 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1033,15 +1450,11 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1054,14 +1467,13 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1074,14 +1486,13 @@
         <v>11</v>
       </c>
       <c r="F13">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="C14">
         <v>7</v>
@@ -1094,14 +1505,13 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1114,14 +1524,13 @@
         <v>13</v>
       </c>
       <c r="F15">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -1134,14 +1543,13 @@
         <v>14</v>
       </c>
       <c r="F16">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1153,15 +1561,11 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1173,15 +1577,11 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="F18">
-        <f t="shared" ref="F18:F29" si="2">F17+1</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -1193,15 +1593,11 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -1210,18 +1606,14 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E20:E30" si="1">E19+1</f>
         <v>18</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -1230,18 +1622,14 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F21">
-        <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -1250,18 +1638,14 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F22">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -1270,18 +1654,14 @@
         <v>20</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F23">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -1290,18 +1670,14 @@
         <v>40</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="F24">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -1310,18 +1686,14 @@
         <v>80</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="F25">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1330,18 +1702,14 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="F26">
-        <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -1350,18 +1718,14 @@
         <v>2</v>
       </c>
       <c r="E27">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -1370,18 +1734,14 @@
         <v>4</v>
       </c>
       <c r="E28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="F28">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1390,15 +1750,11 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
         <v>25</v>
@@ -1410,11 +1766,11 @@
         <v>10</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
         <v>25</v>
@@ -1430,10 +1786,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="B32" t="s">
+        <v>150</v>
+      </c>
       <c r="C32">
         <v>19</v>
       </c>
@@ -1443,9 +1802,15 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
+      <c r="B33" t="s">
+        <v>151</v>
+      </c>
       <c r="C33">
         <v>19</v>
       </c>
@@ -1456,9 +1821,15 @@
         <f>E32+1</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
+      <c r="B34" t="s">
+        <v>152</v>
+      </c>
       <c r="C34">
         <v>19</v>
       </c>
@@ -1466,12 +1837,18 @@
         <v>4</v>
       </c>
       <c r="E34">
-        <f t="shared" ref="E34:E60" si="3">E33+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <f t="shared" ref="E34:E60" si="2">E33+1</f>
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
+      <c r="B35" t="s">
+        <v>153</v>
+      </c>
       <c r="C35">
         <v>19</v>
       </c>
@@ -1479,12 +1856,18 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
       <c r="C36">
         <v>19</v>
       </c>
@@ -1492,12 +1875,15 @@
         <v>10</v>
       </c>
       <c r="E36">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
+      <c r="B37" t="s">
+        <v>154</v>
+      </c>
       <c r="C37">
         <v>19</v>
       </c>
@@ -1505,12 +1891,18 @@
         <v>20</v>
       </c>
       <c r="E37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
+      <c r="B38" t="s">
+        <v>155</v>
+      </c>
       <c r="C38">
         <v>19</v>
       </c>
@@ -1518,12 +1910,18 @@
         <v>40</v>
       </c>
       <c r="E38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
+      <c r="B39" t="s">
+        <v>156</v>
+      </c>
       <c r="C39">
         <v>19</v>
       </c>
@@ -1531,12 +1929,18 @@
         <v>80</v>
       </c>
       <c r="E39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
+      <c r="B40" t="s">
+        <v>157</v>
+      </c>
       <c r="C40">
         <v>18</v>
       </c>
@@ -1544,12 +1948,18 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
       <c r="C41">
         <v>18</v>
       </c>
@@ -1557,14 +1967,14 @@
         <v>2</v>
       </c>
       <c r="E41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="C42">
         <v>18</v>
@@ -1573,20 +1983,14 @@
         <v>4</v>
       </c>
       <c r="E42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="F42">
-        <v>28</v>
-      </c>
-      <c r="G42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="C43">
         <v>18</v>
@@ -1595,16 +1999,15 @@
         <v>8</v>
       </c>
       <c r="E43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="F43">
-        <f>F42+1</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
       <c r="C44">
         <v>18</v>
       </c>
@@ -1612,14 +2015,14 @@
         <v>10</v>
       </c>
       <c r="E44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="C45">
         <v>18</v>
@@ -1628,18 +2031,14 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="F45">
-        <f>F43+1</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C46">
         <v>18</v>
@@ -1648,16 +2047,15 @@
         <v>40</v>
       </c>
       <c r="E46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="F46">
-        <f>F45+1</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
       <c r="C47">
         <v>18</v>
       </c>
@@ -1665,14 +2063,14 @@
         <v>80</v>
       </c>
       <c r="E47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="C48">
         <v>17</v>
@@ -1681,18 +2079,14 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="F48">
-        <f>F46+1</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C49">
         <v>17</v>
@@ -1701,18 +2095,14 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="F49">
-        <f>F48+1</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="C50">
         <v>17</v>
@@ -1721,18 +2111,14 @@
         <v>4</v>
       </c>
       <c r="E50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="F50">
-        <f>F49+1</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C51">
         <v>17</v>
@@ -1741,16 +2127,15 @@
         <v>8</v>
       </c>
       <c r="E51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="F51">
-        <f>F50+1</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
       <c r="C52">
         <v>17</v>
       </c>
@@ -1758,12 +2143,15 @@
         <v>10</v>
       </c>
       <c r="E52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
       <c r="C53">
         <v>17</v>
       </c>
@@ -1771,12 +2159,15 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
       <c r="C54">
         <v>17</v>
       </c>
@@ -1784,11 +2175,11 @@
         <v>40</v>
       </c>
       <c r="E54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
         <v>25</v>
@@ -1800,11 +2191,11 @@
         <v>80</v>
       </c>
       <c r="E55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
         <v>25</v>
@@ -1816,11 +2207,11 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
         <v>25</v>
@@ -1832,11 +2223,11 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
         <v>25</v>
@@ -1848,11 +2239,11 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
         <v>25</v>
@@ -1864,11 +2255,11 @@
         <v>8</v>
       </c>
       <c r="E59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
         <v>25</v>
@@ -1880,11 +2271,11 @@
         <v>10</v>
       </c>
       <c r="E60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" t="s">
         <v>25</v>
@@ -1900,12 +2291,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C62">
         <v>30</v>
@@ -1916,14 +2307,11 @@
       <c r="E62">
         <v>0</v>
       </c>
-      <c r="F62">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="C63">
         <v>30</v>
@@ -1935,15 +2323,11 @@
         <f>E62+1</f>
         <v>1</v>
       </c>
-      <c r="F63">
-        <f>F62+1</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="C64">
         <v>30</v>
@@ -1952,17 +2336,14 @@
         <v>4</v>
       </c>
       <c r="E64">
-        <f t="shared" ref="E64:E90" si="4">E63+1</f>
-        <v>2</v>
-      </c>
-      <c r="F64">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" ref="E64:E79" si="3">E63+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="C65">
         <v>30</v>
@@ -1971,15 +2352,15 @@
         <v>8</v>
       </c>
       <c r="E65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="F65">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
       <c r="C66">
         <v>30</v>
       </c>
@@ -1987,14 +2368,14 @@
         <v>10</v>
       </c>
       <c r="E66">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="C67">
         <v>30</v>
@@ -2003,18 +2384,14 @@
         <v>20</v>
       </c>
       <c r="E67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="F67">
-        <f>F63+1</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="C68">
         <v>30</v>
@@ -2023,18 +2400,14 @@
         <v>40</v>
       </c>
       <c r="E68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="F68">
-        <f>F67+1</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C69">
         <v>30</v>
@@ -2043,22 +2416,15 @@
         <v>80</v>
       </c>
       <c r="E69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="F69">
-        <f>F68+1</f>
-        <v>40</v>
-      </c>
-      <c r="G69">
-        <v>41</v>
-      </c>
-      <c r="H69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
       <c r="C70">
         <v>29</v>
       </c>
@@ -2066,12 +2432,15 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
       <c r="C71">
         <v>29</v>
       </c>
@@ -2079,14 +2448,14 @@
         <v>2</v>
       </c>
       <c r="E71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C72">
         <v>29</v>
@@ -2095,17 +2464,14 @@
         <v>4</v>
       </c>
       <c r="E72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="F72">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C73">
         <v>29</v>
@@ -2114,24 +2480,14 @@
         <v>8</v>
       </c>
       <c r="E73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="F73">
-        <f>F72+1</f>
-        <v>43</v>
-      </c>
-      <c r="G73">
-        <v>44</v>
-      </c>
-      <c r="H73" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C74">
         <v>29</v>
@@ -2140,17 +2496,14 @@
         <v>10</v>
       </c>
       <c r="E74">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="F74">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C75">
         <v>29</v>
@@ -2159,16 +2512,15 @@
         <v>20</v>
       </c>
       <c r="E75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="F75">
-        <f>F74+1</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
       <c r="C76">
         <v>29</v>
       </c>
@@ -2176,14 +2528,14 @@
         <v>40</v>
       </c>
       <c r="E76">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="C77">
         <v>29</v>
@@ -2192,18 +2544,14 @@
         <v>80</v>
       </c>
       <c r="E77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="F77">
-        <f>F75+1</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C78">
         <v>28</v>
@@ -2212,18 +2560,14 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="F78">
-        <f t="shared" ref="F78:F86" si="5">F77+1</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C79">
         <v>28</v>
@@ -2232,18 +2576,14 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="F79">
-        <f t="shared" si="5"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C80">
         <v>28</v>
@@ -2252,18 +2592,14 @@
         <v>4</v>
       </c>
       <c r="E80">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E80:E90" si="4">E79+1</f>
         <v>18</v>
       </c>
-      <c r="F80">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C81">
         <v>28</v>
@@ -2275,15 +2611,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="F81">
-        <f t="shared" si="5"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="C82">
         <v>28</v>
@@ -2295,15 +2627,11 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="F82">
-        <f t="shared" si="5"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="C83">
         <v>28</v>
@@ -2315,15 +2643,11 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="F83">
-        <f t="shared" si="5"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="C84">
         <v>28</v>
@@ -2335,15 +2659,11 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="F84">
-        <f t="shared" si="5"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="C85">
         <v>28</v>
@@ -2355,15 +2675,11 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="F85">
-        <f t="shared" si="5"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C86">
         <v>27</v>
@@ -2375,12 +2691,8 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="F86">
-        <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" t="s">
         <v>25</v>
@@ -2396,7 +2708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" t="s">
         <v>25</v>
@@ -2412,7 +2724,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" t="s">
         <v>25</v>
@@ -2428,7 +2740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" t="s">
         <v>25</v>
@@ -2444,7 +2756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" t="s">
         <v>25</v>
@@ -2460,142 +2772,125 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B92" t="s">
         <v>109</v>
       </c>
-      <c r="F92">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" t="s">
         <v>110</v>
       </c>
-      <c r="F93">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" t="s">
         <v>111</v>
       </c>
-      <c r="F94">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" t="s">
         <v>112</v>
       </c>
-      <c r="F95">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D97" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D98" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
-        <v>78</v>
-      </c>
+      <c r="D99" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C100" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>69</v>
-      </c>
-      <c r="B101" t="s">
-        <v>79</v>
-      </c>
+      <c r="D100" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C101" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B102" t="s">
-        <v>80</v>
-      </c>
+      <c r="D101" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="D102" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="1"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
-      <c r="F106" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="5" t="s">
-        <v>108</v>
-      </c>
+      <c r="F106" s="3"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="3"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+    </row>
+    <row r="112" spans="1:12" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
       <c r="D112" s="5"/>
@@ -2613,8 +2908,8 @@
     <mergeCell ref="A2:A31"/>
     <mergeCell ref="A32:A61"/>
     <mergeCell ref="A62:A91"/>
+    <mergeCell ref="A92:A95"/>
     <mergeCell ref="A112:L112"/>
-    <mergeCell ref="A92:A95"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2622,18 +2917,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AF7111-1B37-497D-B08D-3EB3AFC0EDCF}">
-  <dimension ref="A1:F106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D25623C-CB7E-43B5-9444-FC757D6B6CE6}">
+  <dimension ref="A1:O112"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2647,13 +2947,2868 @@
         <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f>G2+1</f>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f>H2+1</f>
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G30" si="0">G3+1</f>
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H17" si="1">H3+1</f>
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="K9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="K13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="K14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="K15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="K16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>170</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18:H29" si="2">H17+1</f>
+        <v>16</v>
+      </c>
+      <c r="K18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="K19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="K20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="K21" t="s">
+        <v>180</v>
+      </c>
+      <c r="L21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="K22" t="s">
+        <v>180</v>
+      </c>
+      <c r="L22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>180</v>
+      </c>
+      <c r="L23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>180</v>
+      </c>
+      <c r="L24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="K25" t="s">
+        <v>180</v>
+      </c>
+      <c r="L25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="K26" t="s">
+        <v>177</v>
+      </c>
+      <c r="L26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>177</v>
+      </c>
+      <c r="L27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="K28" t="s">
+        <v>184</v>
+      </c>
+      <c r="L28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="K29" t="s">
+        <v>185</v>
+      </c>
+      <c r="L29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <f>G30+1</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32">
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>59</v>
+      </c>
+      <c r="K32" t="s">
+        <v>186</v>
+      </c>
+      <c r="L32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33">
+        <v>19</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <f>G32+1</f>
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>60</v>
+      </c>
+      <c r="K33" t="s">
+        <v>186</v>
+      </c>
+      <c r="L33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34">
+        <v>19</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <f t="shared" ref="G34:G56" si="3">G33+1</f>
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>61</v>
+      </c>
+      <c r="K34" t="s">
+        <v>186</v>
+      </c>
+      <c r="L34" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
+        <v>167</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>62</v>
+      </c>
+      <c r="K35" t="s">
+        <v>186</v>
+      </c>
+      <c r="L35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36">
+        <v>19</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>63</v>
+      </c>
+      <c r="K36" t="s">
+        <v>186</v>
+      </c>
+      <c r="L36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37">
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>64</v>
+      </c>
+      <c r="K37" t="s">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s">
+        <v>179</v>
+      </c>
+      <c r="N37" s="21"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38">
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>40</v>
+      </c>
+      <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>65</v>
+      </c>
+      <c r="K38" t="s">
+        <v>187</v>
+      </c>
+      <c r="L38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>80</v>
+      </c>
+      <c r="E39" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="H39">
+        <v>66</v>
+      </c>
+      <c r="K39" t="s">
+        <v>187</v>
+      </c>
+      <c r="L39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="C40">
+        <v>18</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="K40" t="s">
+        <v>187</v>
+      </c>
+      <c r="L40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="C41">
+        <v>18</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="K41" t="s">
+        <v>187</v>
+      </c>
+      <c r="L41" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42">
+        <v>18</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
+        <v>169</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="H42">
+        <v>28</v>
+      </c>
+      <c r="I42" t="s">
+        <v>104</v>
+      </c>
+      <c r="K42" t="s">
+        <v>188</v>
+      </c>
+      <c r="L42" t="s">
+        <v>179</v>
+      </c>
+      <c r="N42" s="21"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43">
+        <v>18</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="H43">
+        <f>H42+1</f>
+        <v>29</v>
+      </c>
+      <c r="K43" t="s">
+        <v>188</v>
+      </c>
+      <c r="L43" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="C44">
+        <v>18</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>169</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="K44" t="s">
+        <v>188</v>
+      </c>
+      <c r="L44" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>18</v>
+      </c>
+      <c r="D45">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H45">
+        <f>H43+1</f>
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>188</v>
+      </c>
+      <c r="L45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>18</v>
+      </c>
+      <c r="D46">
+        <v>40</v>
+      </c>
+      <c r="E46" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="H46">
+        <f>H45+1</f>
+        <v>31</v>
+      </c>
+      <c r="K46" t="s">
+        <v>188</v>
+      </c>
+      <c r="L46" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="C47">
+        <v>18</v>
+      </c>
+      <c r="D47">
+        <v>80</v>
+      </c>
+      <c r="E47" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="K47" t="s">
+        <v>189</v>
+      </c>
+      <c r="L47" t="s">
+        <v>179</v>
+      </c>
+      <c r="N47" s="21"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>170</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="H48">
+        <f>H46+1</f>
+        <v>32</v>
+      </c>
+      <c r="K48" t="s">
+        <v>189</v>
+      </c>
+      <c r="L48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49">
+        <v>17</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="H49">
+        <f>H48+1</f>
+        <v>33</v>
+      </c>
+      <c r="K49" t="s">
+        <v>189</v>
+      </c>
+      <c r="L49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50">
+        <v>17</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="H50">
+        <f>H49+1</f>
+        <v>34</v>
+      </c>
+      <c r="K50" t="s">
+        <v>189</v>
+      </c>
+      <c r="L50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="H51">
+        <f>H50+1</f>
+        <v>35</v>
+      </c>
+      <c r="K51" t="s">
+        <v>189</v>
+      </c>
+      <c r="L51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+      <c r="B52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="H52">
+        <v>67</v>
+      </c>
+      <c r="K52" t="s">
+        <v>190</v>
+      </c>
+      <c r="L52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+      <c r="B53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53">
+        <v>17</v>
+      </c>
+      <c r="D53">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>171</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="H53">
+        <v>68</v>
+      </c>
+      <c r="K53" t="s">
+        <v>190</v>
+      </c>
+      <c r="L53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="4"/>
+      <c r="B54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54">
+        <v>17</v>
+      </c>
+      <c r="D54">
+        <v>40</v>
+      </c>
+      <c r="E54" t="s">
+        <v>171</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="H54">
+        <v>69</v>
+      </c>
+      <c r="K54" t="s">
+        <v>190</v>
+      </c>
+      <c r="L54">
+        <v>3</v>
+      </c>
+      <c r="N54" s="21"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="4"/>
+      <c r="B55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55">
+        <v>17</v>
+      </c>
+      <c r="D55">
+        <v>80</v>
+      </c>
+      <c r="E55" t="s">
+        <v>171</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H55">
+        <v>70</v>
+      </c>
+      <c r="K55" t="s">
+        <v>190</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+      <c r="B56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56">
+        <v>16</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="H56">
+        <v>71</v>
+      </c>
+      <c r="K56" t="s">
+        <v>190</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="B57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57">
+        <v>16</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="4"/>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58">
+        <v>16</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="4"/>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59">
+        <v>16</v>
+      </c>
+      <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="4"/>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="4"/>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61">
+        <v>16</v>
+      </c>
+      <c r="D61">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>167</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>36</v>
+      </c>
+      <c r="K62" t="s">
+        <v>186</v>
+      </c>
+      <c r="L62" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="4"/>
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63">
+        <v>30</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>167</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <f>G62+1</f>
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <f>H62+1</f>
+        <v>37</v>
+      </c>
+      <c r="K63" t="s">
+        <v>186</v>
+      </c>
+      <c r="L63" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="4"/>
+      <c r="B64" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64">
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64" t="s">
+        <v>167</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <f t="shared" ref="G64:G86" si="4">G63+1</f>
+        <v>2</v>
+      </c>
+      <c r="H64">
+        <v>57</v>
+      </c>
+      <c r="K64" t="s">
+        <v>186</v>
+      </c>
+      <c r="L64" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="4"/>
+      <c r="B65" t="s">
+        <v>118</v>
+      </c>
+      <c r="C65">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>8</v>
+      </c>
+      <c r="E65" t="s">
+        <v>167</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H65">
+        <v>58</v>
+      </c>
+      <c r="K65" t="s">
+        <v>186</v>
+      </c>
+      <c r="L65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="4"/>
+      <c r="C66">
+        <v>30</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K66" t="s">
+        <v>186</v>
+      </c>
+      <c r="L66" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="4"/>
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67">
+        <v>30</v>
+      </c>
+      <c r="D67">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
+        <v>168</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H67">
+        <f>H63+1</f>
+        <v>38</v>
+      </c>
+      <c r="K67" t="s">
+        <v>187</v>
+      </c>
+      <c r="L67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="4"/>
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68">
+        <v>30</v>
+      </c>
+      <c r="D68">
+        <v>40</v>
+      </c>
+      <c r="E68" t="s">
+        <v>168</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H68">
+        <f>H67+1</f>
+        <v>39</v>
+      </c>
+      <c r="K68" t="s">
+        <v>187</v>
+      </c>
+      <c r="L68" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="4"/>
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69">
+        <v>30</v>
+      </c>
+      <c r="D69">
+        <v>80</v>
+      </c>
+      <c r="E69" t="s">
+        <v>168</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H69">
+        <f>H68+1</f>
+        <v>40</v>
+      </c>
+      <c r="I69">
+        <v>41</v>
+      </c>
+      <c r="J69" t="s">
+        <v>106</v>
+      </c>
+      <c r="K69" t="s">
+        <v>187</v>
+      </c>
+      <c r="L69" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="4"/>
+      <c r="C70">
+        <v>29</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>168</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="K70" t="s">
+        <v>187</v>
+      </c>
+      <c r="L70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="4"/>
+      <c r="C71">
+        <v>29</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71" t="s">
+        <v>168</v>
+      </c>
+      <c r="F71">
+        <v>4</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="K71" t="s">
+        <v>187</v>
+      </c>
+      <c r="L71" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="4"/>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72">
+        <v>29</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>169</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="H72">
+        <v>42</v>
+      </c>
+      <c r="K72" t="s">
+        <v>188</v>
+      </c>
+      <c r="L72" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="4"/>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73">
+        <v>29</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>169</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="H73">
+        <f>H72+1</f>
+        <v>43</v>
+      </c>
+      <c r="I73">
+        <v>44</v>
+      </c>
+      <c r="J73" t="s">
+        <v>107</v>
+      </c>
+      <c r="K73" t="s">
+        <v>188</v>
+      </c>
+      <c r="L73" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="4"/>
+      <c r="B74" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74">
+        <v>29</v>
+      </c>
+      <c r="D74">
+        <v>10</v>
+      </c>
+      <c r="E74" t="s">
+        <v>169</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="H74">
+        <v>45</v>
+      </c>
+      <c r="K74" t="s">
+        <v>188</v>
+      </c>
+      <c r="L74" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="4"/>
+      <c r="B75" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75">
+        <v>29</v>
+      </c>
+      <c r="D75">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>169</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="H75">
+        <f>H74+1</f>
+        <v>46</v>
+      </c>
+      <c r="K75" t="s">
+        <v>188</v>
+      </c>
+      <c r="L75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="4"/>
+      <c r="C76">
+        <v>29</v>
+      </c>
+      <c r="D76">
+        <v>40</v>
+      </c>
+      <c r="E76" t="s">
+        <v>169</v>
+      </c>
+      <c r="F76">
+        <v>4</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K76" t="s">
+        <v>188</v>
+      </c>
+      <c r="L76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="4"/>
+      <c r="B77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C77">
+        <v>29</v>
+      </c>
+      <c r="D77">
+        <v>80</v>
+      </c>
+      <c r="E77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="H77">
+        <f>H75+1</f>
+        <v>47</v>
+      </c>
+      <c r="K77" t="s">
+        <v>189</v>
+      </c>
+      <c r="L77" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="4"/>
+      <c r="B78" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78">
+        <v>28</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ref="H78:H86" si="5">H77+1</f>
+        <v>48</v>
+      </c>
+      <c r="K78" t="s">
+        <v>189</v>
+      </c>
+      <c r="L78" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="4"/>
+      <c r="B79" t="s">
+        <v>60</v>
+      </c>
+      <c r="C79">
+        <v>28</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79" t="s">
+        <v>170</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="K79" t="s">
+        <v>189</v>
+      </c>
+      <c r="L79" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="4"/>
+      <c r="B80" t="s">
+        <v>59</v>
+      </c>
+      <c r="C80">
+        <v>28</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="K80" t="s">
+        <v>189</v>
+      </c>
+      <c r="L80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="4"/>
+      <c r="B81" t="s">
+        <v>58</v>
+      </c>
+      <c r="C81">
+        <v>28</v>
+      </c>
+      <c r="D81">
+        <v>8</v>
+      </c>
+      <c r="E81" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81">
+        <v>4</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>51</v>
+      </c>
+      <c r="K81" t="s">
+        <v>189</v>
+      </c>
+      <c r="L81" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="4"/>
+      <c r="B82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="K82" t="s">
+        <v>190</v>
+      </c>
+      <c r="L82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="4"/>
+      <c r="B83" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83">
+        <v>28</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>53</v>
+      </c>
+      <c r="K83" t="s">
+        <v>190</v>
+      </c>
+      <c r="L83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="4"/>
+      <c r="B84" t="s">
+        <v>87</v>
+      </c>
+      <c r="C84">
+        <v>28</v>
+      </c>
+      <c r="D84">
+        <v>40</v>
+      </c>
+      <c r="E84" t="s">
+        <v>171</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="K84" t="s">
+        <v>190</v>
+      </c>
+      <c r="L84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="4"/>
+      <c r="B85" t="s">
+        <v>92</v>
+      </c>
+      <c r="C85">
+        <v>28</v>
+      </c>
+      <c r="D85">
+        <v>80</v>
+      </c>
+      <c r="E85" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="K85" t="s">
+        <v>190</v>
+      </c>
+      <c r="L85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="4"/>
+      <c r="B86" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86">
+        <v>27</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86">
+        <v>4</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+      <c r="K86" t="s">
+        <v>190</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="4"/>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87">
+        <v>27</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="4"/>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88">
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="4"/>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89">
+        <v>27</v>
+      </c>
+      <c r="D89">
+        <v>8</v>
+      </c>
+      <c r="E89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="4"/>
+      <c r="B90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90">
+        <v>27</v>
+      </c>
+      <c r="D90">
+        <v>10</v>
+      </c>
+      <c r="E90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="4"/>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91">
+        <v>27</v>
+      </c>
+      <c r="D91">
+        <v>20</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B92" t="s">
+        <v>109</v>
+      </c>
+      <c r="H92">
+        <v>90</v>
+      </c>
+      <c r="K92" t="s">
+        <v>191</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="4"/>
+      <c r="B93" t="s">
+        <v>110</v>
+      </c>
+      <c r="H93">
+        <v>91</v>
+      </c>
+      <c r="K93" t="s">
+        <v>191</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="4"/>
+      <c r="B94" t="s">
+        <v>111</v>
+      </c>
+      <c r="H94">
+        <v>92</v>
+      </c>
+      <c r="K94" t="s">
+        <v>192</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="4"/>
+      <c r="B95" t="s">
+        <v>112</v>
+      </c>
+      <c r="H95">
+        <v>93</v>
+      </c>
+      <c r="K95" t="s">
+        <v>192</v>
+      </c>
+      <c r="L95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>66</v>
+      </c>
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D97" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D98" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" t="s">
+        <v>76</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D99" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>78</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D100" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>69</v>
+      </c>
+      <c r="B101" t="s">
+        <v>79</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D101" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>80</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D102" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A31"/>
+    <mergeCell ref="A32:A61"/>
+    <mergeCell ref="A62:A91"/>
+    <mergeCell ref="A112:O112"/>
+    <mergeCell ref="A92:A95"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AF7111-1B37-497D-B08D-3EB3AFC0EDCF}">
+  <dimension ref="A1:K106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>117</v>
       </c>
@@ -2666,14 +5821,23 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>0</v>
+      <c r="E2" t="s">
+        <v>167</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" t="s">
         <v>5</v>
@@ -2684,16 +5848,25 @@
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <f>E2+1</f>
-        <v>1</v>
+      <c r="E3" t="s">
+        <v>167</v>
       </c>
       <c r="F3">
-        <f>F2+1</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f>G2+1</f>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f>H2+1</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
         <v>6</v>
@@ -2704,16 +5877,25 @@
       <c r="D4">
         <v>4</v>
       </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E30" si="0">E3+1</f>
-        <v>2</v>
+      <c r="E4" t="s">
+        <v>167</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F24" si="1">F3+1</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G30" si="0">G3+1</f>
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H24" si="1">H3+1</f>
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" t="s">
         <v>7</v>
@@ -2724,16 +5906,25 @@
       <c r="D5">
         <v>8</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
         <v>8</v>
@@ -2744,16 +5935,25 @@
       <c r="D6">
         <v>10</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" t="s">
         <v>9</v>
@@ -2764,16 +5964,25 @@
       <c r="D7">
         <v>20</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" t="s">
         <v>10</v>
@@ -2784,16 +5993,25 @@
       <c r="D8">
         <v>40</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" t="s">
         <v>11</v>
@@ -2804,16 +6022,25 @@
       <c r="D9">
         <v>80</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" t="s">
         <v>12</v>
@@ -2824,16 +6051,25 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" t="s">
         <v>13</v>
@@ -2844,16 +6080,25 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
         <v>14</v>
@@ -2864,16 +6109,25 @@
       <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
         <v>15</v>
@@ -2884,16 +6138,25 @@
       <c r="D13">
         <v>8</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" t="s">
         <v>16</v>
@@ -2904,16 +6167,25 @@
       <c r="D14">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
         <v>17</v>
@@ -2924,16 +6196,25 @@
       <c r="D15">
         <v>20</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
         <v>18</v>
@@ -2944,16 +6225,25 @@
       <c r="D16">
         <v>40</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" t="s">
         <v>19</v>
@@ -2964,16 +6254,25 @@
       <c r="D17">
         <v>80</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="s">
+        <v>170</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
         <v>20</v>
@@ -2984,16 +6283,25 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
         <v>21</v>
@@ -3004,16 +6312,25 @@
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" t="s">
         <v>22</v>
@@ -3024,16 +6341,25 @@
       <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
         <v>23</v>
@@ -3044,16 +6370,25 @@
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
         <v>24</v>
@@ -3064,16 +6399,28 @@
       <c r="D22">
         <v>10</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>193</v>
+      </c>
+      <c r="K22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" t="s">
         <v>24</v>
@@ -3084,16 +6431,28 @@
       <c r="D23">
         <v>20</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>193</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" t="s">
         <v>24</v>
@@ -3104,16 +6463,28 @@
       <c r="D24">
         <v>40</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>193</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" t="s">
         <v>25</v>
@@ -3124,12 +6495,24 @@
       <c r="D25">
         <v>80</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>193</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" t="s">
         <v>25</v>
@@ -3140,12 +6523,24 @@
       <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" t="s">
         <v>25</v>
@@ -3156,12 +6551,18 @@
       <c r="D27">
         <v>2</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" t="s">
         <v>25</v>
@@ -3172,12 +6573,18 @@
       <c r="D28">
         <v>4</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" t="s">
         <v>25</v>
@@ -3188,12 +6595,18 @@
       <c r="D29">
         <v>8</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" t="s">
         <v>25</v>
@@ -3204,12 +6617,18 @@
       <c r="D30">
         <v>10</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" t="s">
         <v>25</v>
@@ -3220,12 +6639,18 @@
       <c r="D31">
         <v>20</v>
       </c>
-      <c r="E31">
-        <f>E30+1</f>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <f>G30+1</f>
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>116</v>
       </c>
@@ -3238,14 +6663,23 @@
       <c r="D32">
         <v>1</v>
       </c>
-      <c r="E32">
-        <v>0</v>
+      <c r="E32" t="s">
+        <v>167</v>
       </c>
       <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>46</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" t="s">
         <v>5</v>
@@ -3256,16 +6690,25 @@
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33">
-        <f>E32+1</f>
-        <v>1</v>
+      <c r="E33" t="s">
+        <v>167</v>
       </c>
       <c r="F33">
-        <f>F32+1</f>
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <f>G32+1</f>
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <f>H32+1</f>
         <v>47</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" t="s">
         <v>6</v>
@@ -3276,16 +6719,25 @@
       <c r="D34">
         <v>4</v>
       </c>
-      <c r="E34">
-        <f t="shared" ref="E34:E60" si="2">E33+1</f>
-        <v>2</v>
+      <c r="E34" t="s">
+        <v>167</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34:F54" si="3">F33+1</f>
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <f t="shared" ref="G34:G60" si="2">G33+1</f>
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <f t="shared" ref="H34:H54" si="3">H33+1</f>
         <v>48</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" t="s">
         <v>7</v>
@@ -3296,16 +6748,25 @@
       <c r="D35">
         <v>8</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="s">
+        <v>167</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" t="s">
         <v>8</v>
@@ -3316,16 +6777,25 @@
       <c r="D36">
         <v>10</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" t="s">
         <v>9</v>
@@ -3336,16 +6806,25 @@
       <c r="D37">
         <v>20</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" t="s">
         <v>10</v>
@@ -3356,16 +6835,25 @@
       <c r="D38">
         <v>40</v>
       </c>
-      <c r="E38">
+      <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J38" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" t="s">
         <v>11</v>
@@ -3376,16 +6864,25 @@
       <c r="D39">
         <v>80</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J39" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" t="s">
         <v>12</v>
@@ -3396,16 +6893,25 @@
       <c r="D40">
         <v>1</v>
       </c>
-      <c r="E40">
+      <c r="E40" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" t="s">
         <v>13</v>
@@ -3416,16 +6922,25 @@
       <c r="D41">
         <v>2</v>
       </c>
-      <c r="E41">
+      <c r="E41" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" t="s">
         <v>14</v>
@@ -3436,16 +6951,25 @@
       <c r="D42">
         <v>4</v>
       </c>
-      <c r="E42">
+      <c r="E42" t="s">
+        <v>169</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" t="s">
         <v>15</v>
@@ -3456,16 +6980,25 @@
       <c r="D43">
         <v>8</v>
       </c>
-      <c r="E43">
+      <c r="E43" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J43" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" t="s">
         <v>16</v>
@@ -3476,16 +7009,25 @@
       <c r="D44">
         <v>10</v>
       </c>
-      <c r="E44">
+      <c r="E44" t="s">
+        <v>169</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" t="s">
         <v>17</v>
@@ -3496,16 +7038,25 @@
       <c r="D45">
         <v>20</v>
       </c>
-      <c r="E45">
+      <c r="E45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="F45">
+      <c r="H45">
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" t="s">
         <v>18</v>
@@ -3516,16 +7067,25 @@
       <c r="D46">
         <v>40</v>
       </c>
-      <c r="E46">
+      <c r="E46" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" t="s">
         <v>19</v>
@@ -3536,16 +7096,25 @@
       <c r="D47">
         <v>80</v>
       </c>
-      <c r="E47">
+      <c r="E47" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" t="s">
         <v>20</v>
@@ -3556,16 +7125,25 @@
       <c r="D48">
         <v>1</v>
       </c>
-      <c r="E48">
+      <c r="E48" t="s">
+        <v>170</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <f t="shared" si="3"/>
         <v>62</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" t="s">
         <v>21</v>
@@ -3576,16 +7154,25 @@
       <c r="D49">
         <v>2</v>
       </c>
-      <c r="E49">
+      <c r="E49" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" t="s">
         <v>22</v>
@@ -3596,16 +7183,25 @@
       <c r="D50">
         <v>4</v>
       </c>
-      <c r="E50">
+      <c r="E50" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" t="s">
         <v>23</v>
@@ -3616,16 +7212,25 @@
       <c r="D51">
         <v>8</v>
       </c>
-      <c r="E51">
+      <c r="E51" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="G51">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="F51">
+      <c r="H51">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" t="s">
         <v>24</v>
@@ -3636,16 +7241,28 @@
       <c r="D52">
         <v>10</v>
       </c>
-      <c r="E52">
+      <c r="E52" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="F52">
+      <c r="H52">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>193</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" t="s">
         <v>24</v>
@@ -3656,16 +7273,28 @@
       <c r="D53">
         <v>20</v>
       </c>
-      <c r="E53">
+      <c r="E53" t="s">
+        <v>171</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="F53">
+      <c r="H53">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>193</v>
+      </c>
+      <c r="K53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" t="s">
         <v>24</v>
@@ -3676,16 +7305,28 @@
       <c r="D54">
         <v>40</v>
       </c>
-      <c r="E54">
+      <c r="E54" t="s">
+        <v>171</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="F54">
+      <c r="H54">
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>193</v>
+      </c>
+      <c r="K54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" t="s">
         <v>25</v>
@@ -3696,12 +7337,24 @@
       <c r="D55">
         <v>80</v>
       </c>
-      <c r="E55">
+      <c r="E55" t="s">
+        <v>171</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J55" t="s">
+        <v>193</v>
+      </c>
+      <c r="K55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
         <v>25</v>
@@ -3712,12 +7365,24 @@
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="E56">
+      <c r="E56" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>193</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
         <v>25</v>
@@ -3728,12 +7393,15 @@
       <c r="D57">
         <v>2</v>
       </c>
-      <c r="E57">
+      <c r="E57" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" t="s">
         <v>25</v>
@@ -3744,12 +7412,15 @@
       <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58">
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" t="s">
         <v>25</v>
@@ -3760,12 +7431,15 @@
       <c r="D59">
         <v>8</v>
       </c>
-      <c r="E59">
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" t="s">
         <v>25</v>
@@ -3776,12 +7450,15 @@
       <c r="D60">
         <v>10</v>
       </c>
-      <c r="E60">
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" t="s">
         <v>25</v>
@@ -3792,12 +7469,15 @@
       <c r="D61">
         <v>20</v>
       </c>
-      <c r="E61">
-        <f>E60+1</f>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61">
+        <f>G60+1</f>
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>115</v>
       </c>
@@ -3810,14 +7490,23 @@
       <c r="D62">
         <v>1</v>
       </c>
-      <c r="E62">
-        <v>0</v>
+      <c r="E62" t="s">
+        <v>167</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" t="s">
         <v>5</v>
@@ -3828,16 +7517,25 @@
       <c r="D63">
         <v>2</v>
       </c>
-      <c r="E63">
-        <f>E62+1</f>
-        <v>1</v>
+      <c r="E63" t="s">
+        <v>167</v>
       </c>
       <c r="F63">
-        <f>F62+1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <f>G62+1</f>
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <f>H62+1</f>
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" t="s">
         <v>6</v>
@@ -3848,16 +7546,25 @@
       <c r="D64">
         <v>4</v>
       </c>
-      <c r="E64">
-        <f t="shared" ref="E64:E90" si="4">E63+1</f>
-        <v>2</v>
+      <c r="E64" t="s">
+        <v>167</v>
       </c>
       <c r="F64">
-        <f t="shared" ref="F64:F84" si="5">F63+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <f t="shared" ref="G64:G90" si="4">G63+1</f>
+        <v>2</v>
+      </c>
+      <c r="H64">
+        <f t="shared" ref="H64:H84" si="5">H63+1</f>
+        <v>2</v>
+      </c>
+      <c r="J64" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" t="s">
         <v>7</v>
@@ -3868,16 +7575,25 @@
       <c r="D65">
         <v>8</v>
       </c>
-      <c r="E65">
+      <c r="E65" t="s">
+        <v>167</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F65">
+      <c r="H65">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" t="s">
         <v>8</v>
@@ -3888,16 +7604,25 @@
       <c r="D66">
         <v>10</v>
       </c>
-      <c r="E66">
+      <c r="E66" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F66">
+      <c r="H66">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J66" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" t="s">
         <v>23</v>
@@ -3908,16 +7633,25 @@
       <c r="D67">
         <v>20</v>
       </c>
-      <c r="E67">
+      <c r="E67" t="s">
+        <v>168</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J67" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" t="s">
         <v>22</v>
@@ -3928,16 +7662,25 @@
       <c r="D68">
         <v>40</v>
       </c>
-      <c r="E68">
+      <c r="E68" t="s">
+        <v>168</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F68">
+      <c r="H68">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J68" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" t="s">
         <v>21</v>
@@ -3948,16 +7691,25 @@
       <c r="D69">
         <v>80</v>
       </c>
-      <c r="E69">
+      <c r="E69" t="s">
+        <v>168</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F69">
+      <c r="H69">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J69" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" t="s">
         <v>20</v>
@@ -3968,16 +7720,25 @@
       <c r="D70">
         <v>1</v>
       </c>
-      <c r="E70">
+      <c r="E70" t="s">
+        <v>168</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F70">
+      <c r="H70">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J70" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" t="s">
         <v>19</v>
@@ -3988,16 +7749,25 @@
       <c r="D71">
         <v>2</v>
       </c>
-      <c r="E71">
+      <c r="E71" t="s">
+        <v>168</v>
+      </c>
+      <c r="F71">
+        <v>4</v>
+      </c>
+      <c r="G71">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F71">
+      <c r="H71">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" t="s">
         <v>18</v>
@@ -4008,16 +7778,25 @@
       <c r="D72">
         <v>4</v>
       </c>
-      <c r="E72">
+      <c r="E72" t="s">
+        <v>169</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F72">
+      <c r="H72">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" t="s">
         <v>17</v>
@@ -4028,16 +7807,25 @@
       <c r="D73">
         <v>8</v>
       </c>
-      <c r="E73">
+      <c r="E73" t="s">
+        <v>169</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F73">
+      <c r="H73">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J73" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" t="s">
         <v>16</v>
@@ -4048,16 +7836,25 @@
       <c r="D74">
         <v>10</v>
       </c>
-      <c r="E74">
+      <c r="E74" t="s">
+        <v>169</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F74">
+      <c r="H74">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J74" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" t="s">
         <v>15</v>
@@ -4068,16 +7865,25 @@
       <c r="D75">
         <v>20</v>
       </c>
-      <c r="E75">
+      <c r="E75" t="s">
+        <v>169</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="F75">
+      <c r="H75">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J75" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" t="s">
         <v>14</v>
@@ -4088,16 +7894,25 @@
       <c r="D76">
         <v>40</v>
       </c>
-      <c r="E76">
+      <c r="E76" t="s">
+        <v>169</v>
+      </c>
+      <c r="F76">
+        <v>4</v>
+      </c>
+      <c r="G76">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="F76">
+      <c r="H76">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J76" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" t="s">
         <v>9</v>
@@ -4108,16 +7923,25 @@
       <c r="D77">
         <v>80</v>
       </c>
-      <c r="E77">
+      <c r="E77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J77" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" t="s">
         <v>10</v>
@@ -4128,16 +7952,25 @@
       <c r="D78">
         <v>1</v>
       </c>
-      <c r="E78">
+      <c r="E78" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J78" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" t="s">
         <v>11</v>
@@ -4148,16 +7981,25 @@
       <c r="D79">
         <v>2</v>
       </c>
-      <c r="E79">
+      <c r="E79" t="s">
+        <v>170</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="F79">
+      <c r="H79">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J79" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" t="s">
         <v>12</v>
@@ -4168,16 +8010,25 @@
       <c r="D80">
         <v>4</v>
       </c>
-      <c r="E80">
+      <c r="E80" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="F80">
+      <c r="H80">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J80" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" t="s">
         <v>13</v>
@@ -4188,16 +8039,25 @@
       <c r="D81">
         <v>8</v>
       </c>
-      <c r="E81">
+      <c r="E81" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81">
+        <v>4</v>
+      </c>
+      <c r="G81">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="F81">
+      <c r="H81">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J81" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" t="s">
         <v>24</v>
@@ -4208,16 +8068,28 @@
       <c r="D82">
         <v>10</v>
       </c>
-      <c r="E82">
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="F82">
+      <c r="H82">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>193</v>
+      </c>
+      <c r="K82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" t="s">
         <v>24</v>
@@ -4228,16 +8100,28 @@
       <c r="D83">
         <v>20</v>
       </c>
-      <c r="E83">
+      <c r="E83" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="F83">
+      <c r="H83">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J83" t="s">
+        <v>193</v>
+      </c>
+      <c r="K83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" t="s">
         <v>24</v>
@@ -4248,16 +8132,28 @@
       <c r="D84">
         <v>40</v>
       </c>
-      <c r="E84">
+      <c r="E84" t="s">
+        <v>171</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="F84">
+      <c r="H84">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J84" t="s">
+        <v>193</v>
+      </c>
+      <c r="K84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" t="s">
         <v>25</v>
@@ -4268,12 +8164,24 @@
       <c r="D85">
         <v>80</v>
       </c>
-      <c r="E85">
+      <c r="E85" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J85" t="s">
+        <v>193</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" t="s">
         <v>25</v>
@@ -4284,12 +8192,24 @@
       <c r="D86">
         <v>1</v>
       </c>
-      <c r="E86">
+      <c r="E86" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86">
+        <v>4</v>
+      </c>
+      <c r="G86">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J86" t="s">
+        <v>193</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" t="s">
         <v>25</v>
@@ -4300,12 +8220,15 @@
       <c r="D87">
         <v>2</v>
       </c>
-      <c r="E87">
+      <c r="E87" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" t="s">
         <v>25</v>
@@ -4316,12 +8239,15 @@
       <c r="D88">
         <v>4</v>
       </c>
-      <c r="E88">
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="G88">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" t="s">
         <v>25</v>
@@ -4332,12 +8258,15 @@
       <c r="D89">
         <v>8</v>
       </c>
-      <c r="E89">
+      <c r="E89" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" t="s">
         <v>25</v>
@@ -4348,12 +8277,15 @@
       <c r="D90">
         <v>10</v>
       </c>
-      <c r="E90">
+      <c r="E90" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" t="s">
         <v>25</v>
@@ -4364,44 +8296,49 @@
       <c r="D91">
         <v>20</v>
       </c>
-      <c r="E91">
-        <f>E90+1</f>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91">
+        <f>G90+1</f>
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C97" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C98" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C99" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C100" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C101" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4412,4 +8349,592 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7503D4-6FF3-45F4-AB6A-66DA4D90713B}">
+  <dimension ref="B1:CK4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="138" width="4.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B1" s="14">
+        <v>0</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
+        <v>1</v>
+      </c>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
+        <v>2</v>
+      </c>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
+        <v>4</v>
+      </c>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
+        <v>5</v>
+      </c>
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
+        <v>6</v>
+      </c>
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15"/>
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15"/>
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15"/>
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
+        <v>7</v>
+      </c>
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15"/>
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15"/>
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15"/>
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
+        <v>8</v>
+      </c>
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15"/>
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15"/>
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15"/>
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
+        <v>9</v>
+      </c>
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15"/>
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15"/>
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15"/>
+      <c r="CC1" s="16"/>
+      <c r="CD1" s="7"/>
+      <c r="CE1" s="7"/>
+      <c r="CF1" s="7"/>
+      <c r="CG1" s="7"/>
+      <c r="CH1" s="7"/>
+      <c r="CI1" s="7"/>
+      <c r="CJ1" s="7"/>
+      <c r="CK1" s="7"/>
+    </row>
+    <row r="2" spans="2:89" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="17">
+        <v>7</v>
+      </c>
+      <c r="C2" s="18">
+        <v>6</v>
+      </c>
+      <c r="D2" s="18">
+        <v>5</v>
+      </c>
+      <c r="E2" s="18">
+        <v>4</v>
+      </c>
+      <c r="F2" s="18">
+        <v>3</v>
+      </c>
+      <c r="G2" s="18">
+        <v>2</v>
+      </c>
+      <c r="H2" s="18">
+        <v>1</v>
+      </c>
+      <c r="I2" s="18">
+        <v>0</v>
+      </c>
+      <c r="J2" s="18">
+        <v>7</v>
+      </c>
+      <c r="K2" s="18">
+        <v>6</v>
+      </c>
+      <c r="L2" s="18">
+        <v>5</v>
+      </c>
+      <c r="M2" s="18">
+        <v>4</v>
+      </c>
+      <c r="N2" s="18">
+        <v>3</v>
+      </c>
+      <c r="O2" s="18">
+        <v>2</v>
+      </c>
+      <c r="P2" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="18">
+        <v>0</v>
+      </c>
+      <c r="R2" s="18">
+        <v>7</v>
+      </c>
+      <c r="S2" s="18">
+        <v>6</v>
+      </c>
+      <c r="T2" s="18">
+        <v>5</v>
+      </c>
+      <c r="U2" s="18">
+        <v>4</v>
+      </c>
+      <c r="V2" s="18">
+        <v>3</v>
+      </c>
+      <c r="W2" s="18">
+        <v>2</v>
+      </c>
+      <c r="X2" s="18">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="18">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="18">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="18">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="18">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="18">
+        <v>3</v>
+      </c>
+      <c r="AE2" s="18">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="18">
+        <v>7</v>
+      </c>
+      <c r="AI2" s="18">
+        <v>6</v>
+      </c>
+      <c r="AJ2" s="18">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="18">
+        <v>4</v>
+      </c>
+      <c r="AL2" s="18">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="18">
+        <v>2</v>
+      </c>
+      <c r="AN2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="18">
+        <v>7</v>
+      </c>
+      <c r="AQ2" s="18">
+        <v>6</v>
+      </c>
+      <c r="AR2" s="18">
+        <v>5</v>
+      </c>
+      <c r="AS2" s="18">
+        <v>4</v>
+      </c>
+      <c r="AT2" s="18">
+        <v>3</v>
+      </c>
+      <c r="AU2" s="18">
+        <v>2</v>
+      </c>
+      <c r="AV2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="18">
+        <v>7</v>
+      </c>
+      <c r="AY2" s="18">
+        <v>6</v>
+      </c>
+      <c r="AZ2" s="18">
+        <v>5</v>
+      </c>
+      <c r="BA2" s="18">
+        <v>4</v>
+      </c>
+      <c r="BB2" s="18">
+        <v>3</v>
+      </c>
+      <c r="BC2" s="18">
+        <v>2</v>
+      </c>
+      <c r="BD2" s="18">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="18">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="18">
+        <v>7</v>
+      </c>
+      <c r="BG2" s="18">
+        <v>6</v>
+      </c>
+      <c r="BH2" s="18">
+        <v>5</v>
+      </c>
+      <c r="BI2" s="18">
+        <v>4</v>
+      </c>
+      <c r="BJ2" s="18">
+        <v>3</v>
+      </c>
+      <c r="BK2" s="18">
+        <v>2</v>
+      </c>
+      <c r="BL2" s="18">
+        <v>1</v>
+      </c>
+      <c r="BM2" s="18">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="18">
+        <v>7</v>
+      </c>
+      <c r="BO2" s="18">
+        <v>6</v>
+      </c>
+      <c r="BP2" s="18">
+        <v>5</v>
+      </c>
+      <c r="BQ2" s="18">
+        <v>4</v>
+      </c>
+      <c r="BR2" s="18">
+        <v>3</v>
+      </c>
+      <c r="BS2" s="18">
+        <v>2</v>
+      </c>
+      <c r="BT2" s="18">
+        <v>1</v>
+      </c>
+      <c r="BU2" s="18">
+        <v>0</v>
+      </c>
+      <c r="BV2" s="19"/>
+      <c r="BW2" s="19"/>
+      <c r="BX2" s="19"/>
+      <c r="BY2" s="19"/>
+      <c r="BZ2" s="19"/>
+      <c r="CA2" s="19"/>
+      <c r="CB2" s="19"/>
+      <c r="CC2" s="20"/>
+      <c r="CD2" s="6"/>
+      <c r="CE2" s="6"/>
+      <c r="CF2" s="6"/>
+      <c r="CG2" s="6"/>
+      <c r="CH2" s="6"/>
+      <c r="CI2" s="6"/>
+      <c r="CJ2" s="6"/>
+      <c r="CK2" s="6"/>
+    </row>
+    <row r="3" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B3" s="10">
+        <v>0</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="10"/>
+      <c r="AM3" s="10"/>
+      <c r="AN3" s="10"/>
+      <c r="AO3" s="10"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="AS3" s="12"/>
+      <c r="AT3" s="12"/>
+      <c r="AU3" s="12"/>
+      <c r="AV3" s="13"/>
+      <c r="AW3" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AX3" s="10"/>
+      <c r="AY3" s="10"/>
+      <c r="AZ3" s="10"/>
+      <c r="BA3" s="10"/>
+      <c r="BB3" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="BC3" s="10"/>
+      <c r="BD3" s="10"/>
+      <c r="BE3" s="10"/>
+      <c r="BF3" s="10"/>
+      <c r="BG3" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="BH3" s="10"/>
+      <c r="BI3" s="10"/>
+      <c r="BJ3" s="10"/>
+      <c r="BK3" s="10"/>
+      <c r="BL3" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="BM3" s="10"/>
+      <c r="BN3" s="10"/>
+      <c r="BO3" s="10"/>
+      <c r="BP3" s="10"/>
+      <c r="BQ3" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="BR3" s="10"/>
+      <c r="BS3" s="10"/>
+      <c r="BT3" s="10"/>
+      <c r="BU3" s="10"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="9"/>
+      <c r="CA3" s="9"/>
+      <c r="CB3" s="9"/>
+      <c r="CC3" s="9"/>
+    </row>
+    <row r="4" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="8">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AX4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AY4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="8">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="8">
+        <v>4</v>
+      </c>
+      <c r="BC4" s="8">
+        <v>3</v>
+      </c>
+      <c r="BD4" s="8">
+        <v>2</v>
+      </c>
+      <c r="BE4" s="8">
+        <v>1</v>
+      </c>
+      <c r="BF4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="8">
+        <v>4</v>
+      </c>
+      <c r="BH4" s="8">
+        <v>3</v>
+      </c>
+      <c r="BI4" s="8">
+        <v>2</v>
+      </c>
+      <c r="BJ4" s="8">
+        <v>1</v>
+      </c>
+      <c r="BK4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="8">
+        <v>4</v>
+      </c>
+      <c r="BM4" s="8">
+        <v>3</v>
+      </c>
+      <c r="BN4" s="8">
+        <v>2</v>
+      </c>
+      <c r="BO4" s="8">
+        <v>1</v>
+      </c>
+      <c r="BP4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ4" s="8">
+        <v>4</v>
+      </c>
+      <c r="BR4" s="8">
+        <v>3</v>
+      </c>
+      <c r="BS4" s="8">
+        <v>2</v>
+      </c>
+      <c r="BT4" s="8">
+        <v>1</v>
+      </c>
+      <c r="BU4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BV4" s="9"/>
+      <c r="BW4" s="9"/>
+      <c r="BX4" s="9"/>
+      <c r="BY4" s="9"/>
+      <c r="BZ4" s="9"/>
+      <c r="CA4" s="9"/>
+      <c r="CB4" s="9"/>
+      <c r="CC4" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AO3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
+    <mergeCell ref="AX1:BE1"/>
+    <mergeCell ref="BF1:BM1"/>
+    <mergeCell ref="BN1:BU1"/>
+    <mergeCell ref="BV1:CC1"/>
+    <mergeCell ref="CD1:CK1"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
+    <mergeCell ref="AH1:AO1"/>
+    <mergeCell ref="AP1:AW1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Button tables.xlsx
+++ b/Button tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_dummy\cockpit_arduino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CC2DC5-E720-4445-8E99-FF67D7F76533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D8F7A5-3BDF-49B0-BFC7-D4CDE33E31CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="135" windowWidth="45015" windowHeight="7020" activeTab="4" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
+    <workbookView xWindow="33690" yWindow="330" windowWidth="16770" windowHeight="19740" xr2:uid="{B42DDCD9-64C5-4A29-BEC7-73E9BF8FAFC9}"/>
   </bookViews>
   <sheets>
     <sheet name=" Engine Arduino" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="255">
   <si>
     <t>Key</t>
   </si>
@@ -459,9 +459,6 @@
     <t>Jettison 5</t>
   </si>
   <si>
-    <t>HUD Symbol Rej 1</t>
-  </si>
-  <si>
     <t>HUD Symbol Rej 2</t>
   </si>
   <si>
@@ -705,21 +702,6 @@
     <t>INS IFA</t>
   </si>
   <si>
-    <t>INS GYRO</t>
-  </si>
-  <si>
-    <t>INS GB</t>
-  </si>
-  <si>
-    <t>INS Test</t>
-  </si>
-  <si>
-    <t>Light Mode Day</t>
-  </si>
-  <si>
-    <t>Lite Mode NVG</t>
-  </si>
-  <si>
     <t>Radar Off</t>
   </si>
   <si>
@@ -738,9 +720,6 @@
     <t>None means FLIR Stdby</t>
   </si>
   <si>
-    <t>LTD/R AFT</t>
-  </si>
-  <si>
     <t>LTD/R Arm</t>
   </si>
   <si>
@@ -808,6 +787,24 @@
   </si>
   <si>
     <t>Altimeter Rotary Depress</t>
+  </si>
+  <si>
+    <t>Not used</t>
+  </si>
+  <si>
+    <t>HUD Symbol Norm</t>
+  </si>
+  <si>
+    <t>LTD/R Aft</t>
+  </si>
+  <si>
+    <t>Lite Mode Day</t>
+  </si>
+  <si>
+    <t>Light Mode NVG</t>
+  </si>
+  <si>
+    <t>Intetrnal Main = 0</t>
   </si>
 </sst>
 </file>
@@ -1475,22 +1472,22 @@
         <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>86</v>
@@ -1498,7 +1495,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>26</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
         <v>128</v>
@@ -1510,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1522,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1537,7 +1534,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1550,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1565,7 +1562,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1578,7 +1575,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1593,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1606,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1621,7 +1618,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1634,7 +1631,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1649,7 +1646,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1662,14 +1659,11 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="20"/>
-      <c r="B8" t="s">
-        <v>200</v>
-      </c>
       <c r="C8">
         <v>8</v>
       </c>
@@ -1677,7 +1671,7 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1686,21 +1680,15 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H8">
-        <v>11</v>
-      </c>
       <c r="I8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
-      <c r="B9" t="s">
-        <v>199</v>
-      </c>
       <c r="C9">
         <v>8</v>
       </c>
@@ -1708,7 +1696,7 @@
         <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1717,20 +1705,17 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H9">
-        <v>12</v>
-      </c>
       <c r="I9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1739,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1752,16 +1737,16 @@
         <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1770,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -1783,10 +1768,10 @@
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1801,7 +1786,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1814,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1829,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1842,7 +1827,7 @@
         <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1857,7 +1842,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1870,7 +1855,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1885,7 +1870,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1898,7 +1883,7 @@
         <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1913,7 +1898,7 @@
         <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -1926,13 +1911,13 @@
         <v>9</v>
       </c>
       <c r="I16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="20"/>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1941,23 +1926,23 @@
         <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" si="0"/>
+        <f>G16+1</f>
         <v>15</v>
       </c>
       <c r="H17">
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1972,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1985,10 +1970,10 @@
         <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2003,7 +1988,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -2016,16 +2001,16 @@
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="20"/>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>250</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -2034,7 +2019,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -2047,16 +2032,16 @@
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="20"/>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -2065,7 +2050,7 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -2078,16 +2063,16 @@
         <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2096,7 +2081,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2109,16 +2094,16 @@
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -2127,7 +2112,7 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2140,16 +2125,16 @@
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2158,7 +2143,7 @@
         <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -2171,16 +2156,16 @@
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2189,7 +2174,7 @@
         <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -2202,16 +2187,16 @@
         <v>23</v>
       </c>
       <c r="I25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2220,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -2230,10 +2215,10 @@
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2248,7 +2233,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2258,10 +2243,10 @@
         <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2276,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2286,10 +2271,10 @@
         <v>26</v>
       </c>
       <c r="I28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2304,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -2314,16 +2299,16 @@
         <v>27</v>
       </c>
       <c r="I29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="20"/>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -2332,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F30">
         <v>3</v>
@@ -2341,17 +2326,20 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
+      <c r="H30">
+        <v>11</v>
+      </c>
       <c r="I30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="20"/>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -2360,7 +2348,7 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F31">
         <v>4</v>
@@ -2369,11 +2357,14 @@
         <f>G30+1</f>
         <v>29</v>
       </c>
+      <c r="H31">
+        <v>12</v>
+      </c>
       <c r="I31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2384,13 +2375,13 @@
         <v>25</v>
       </c>
       <c r="C32">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2399,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2411,13 +2402,13 @@
         <v>25</v>
       </c>
       <c r="C33">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2427,10 +2418,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2439,13 +2430,13 @@
         <v>25</v>
       </c>
       <c r="C34">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -2455,10 +2446,10 @@
         <v>2</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2467,13 +2458,13 @@
         <v>25</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -2483,10 +2474,10 @@
         <v>3</v>
       </c>
       <c r="I35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2495,13 +2486,13 @@
         <v>25</v>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -2511,10 +2502,10 @@
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2523,13 +2514,13 @@
         <v>25</v>
       </c>
       <c r="C37">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2539,10 +2530,10 @@
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2551,13 +2542,13 @@
         <v>25</v>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2567,10 +2558,10 @@
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2579,13 +2570,13 @@
         <v>25</v>
       </c>
       <c r="C39">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -2595,10 +2586,10 @@
         <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2607,13 +2598,13 @@
         <v>25</v>
       </c>
       <c r="C40">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -2623,10 +2614,10 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2635,13 +2626,13 @@
         <v>25</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -2651,10 +2642,10 @@
         <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2663,13 +2654,13 @@
         <v>25</v>
       </c>
       <c r="C42">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2679,10 +2670,10 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2691,13 +2682,13 @@
         <v>25</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2707,10 +2698,10 @@
         <v>11</v>
       </c>
       <c r="I43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2719,13 +2710,13 @@
         <v>25</v>
       </c>
       <c r="C44">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -2735,10 +2726,10 @@
         <v>12</v>
       </c>
       <c r="I44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2747,13 +2738,13 @@
         <v>25</v>
       </c>
       <c r="C45">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -2763,10 +2754,10 @@
         <v>13</v>
       </c>
       <c r="I45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2775,13 +2766,13 @@
         <v>25</v>
       </c>
       <c r="C46">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -2791,10 +2782,10 @@
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2803,13 +2794,13 @@
         <v>25</v>
       </c>
       <c r="C47">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2819,10 +2810,10 @@
         <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2831,13 +2822,13 @@
         <v>25</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -2847,10 +2838,10 @@
         <v>16</v>
       </c>
       <c r="I48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -2859,13 +2850,13 @@
         <v>25</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D49">
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -2875,10 +2866,10 @@
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2887,13 +2878,13 @@
         <v>25</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -2903,10 +2894,10 @@
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2915,13 +2906,13 @@
         <v>25</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F51">
         <v>4</v>
@@ -2931,10 +2922,10 @@
         <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2943,13 +2934,13 @@
         <v>25</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D52">
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2959,10 +2950,10 @@
         <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J52" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -2971,13 +2962,13 @@
         <v>25</v>
       </c>
       <c r="C53">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D53">
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -2987,10 +2978,10 @@
         <v>21</v>
       </c>
       <c r="I53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2999,13 +2990,13 @@
         <v>25</v>
       </c>
       <c r="C54">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -3015,10 +3006,10 @@
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3027,13 +3018,13 @@
         <v>25</v>
       </c>
       <c r="C55">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>80</v>
       </c>
       <c r="E55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -3043,10 +3034,10 @@
         <v>23</v>
       </c>
       <c r="I55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3055,13 +3046,13 @@
         <v>25</v>
       </c>
       <c r="C56">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -3071,10 +3062,10 @@
         <v>24</v>
       </c>
       <c r="I56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -3083,7 +3074,7 @@
         <v>25</v>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3102,7 +3093,7 @@
         <v>25</v>
       </c>
       <c r="C58">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -3121,7 +3112,7 @@
         <v>25</v>
       </c>
       <c r="C59">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>8</v>
@@ -3140,7 +3131,7 @@
         <v>25</v>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>10</v>
@@ -3159,7 +3150,7 @@
         <v>25</v>
       </c>
       <c r="C61">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>20</v>
@@ -3174,7 +3165,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
         <v>25</v>
@@ -3186,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3195,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3210,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -3219,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -3234,7 +3225,7 @@
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64">
         <v>2</v>
@@ -3243,7 +3234,7 @@
         <v>2</v>
       </c>
       <c r="I64" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -3258,7 +3249,7 @@
         <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -3267,7 +3258,7 @@
         <v>3</v>
       </c>
       <c r="I65" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -3282,7 +3273,7 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F66">
         <v>4</v>
@@ -3291,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="I66" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -3306,7 +3297,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3315,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -3330,7 +3321,7 @@
         <v>40</v>
       </c>
       <c r="E68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -3339,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -3354,7 +3345,7 @@
         <v>80</v>
       </c>
       <c r="E69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F69">
         <v>2</v>
@@ -3363,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="I69" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -3378,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -3387,7 +3378,7 @@
         <v>3</v>
       </c>
       <c r="I70" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -3402,7 +3393,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F71">
         <v>4</v>
@@ -3411,7 +3402,7 @@
         <v>4</v>
       </c>
       <c r="I71" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -3426,7 +3417,7 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3435,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -3450,7 +3441,7 @@
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -3459,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -3474,7 +3465,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -3483,7 +3474,7 @@
         <v>2</v>
       </c>
       <c r="I74" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -3498,7 +3489,7 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -3507,7 +3498,7 @@
         <v>3</v>
       </c>
       <c r="I75" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3522,7 +3513,7 @@
         <v>40</v>
       </c>
       <c r="E76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F76">
         <v>4</v>
@@ -3531,7 +3522,7 @@
         <v>4</v>
       </c>
       <c r="I76" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -3546,7 +3537,7 @@
         <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -3555,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -3570,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -3579,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -3594,7 +3585,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F79">
         <v>2</v>
@@ -3603,7 +3594,7 @@
         <v>2</v>
       </c>
       <c r="I79" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3618,7 +3609,7 @@
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -3627,7 +3618,7 @@
         <v>3</v>
       </c>
       <c r="I80" t="s">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -3642,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F81">
         <v>4</v>
@@ -3651,16 +3642,16 @@
         <v>4</v>
       </c>
       <c r="I81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J81" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="19"/>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C82">
         <v>6</v>
@@ -3669,7 +3660,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3681,16 +3672,16 @@
         <v>24</v>
       </c>
       <c r="I82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J82" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="19"/>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C83">
         <v>6</v>
@@ -3699,7 +3690,7 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -3711,16 +3702,16 @@
         <v>25</v>
       </c>
       <c r="I83" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="19"/>
       <c r="B84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C84">
         <v>6</v>
@@ -3729,7 +3720,7 @@
         <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F84">
         <v>2</v>
@@ -3741,16 +3732,16 @@
         <v>26</v>
       </c>
       <c r="I84" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="19"/>
       <c r="B85" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C85">
         <v>6</v>
@@ -3759,7 +3750,7 @@
         <v>80</v>
       </c>
       <c r="E85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F85">
         <v>3</v>
@@ -3771,16 +3762,16 @@
         <v>27</v>
       </c>
       <c r="I85" t="s">
+        <v>168</v>
+      </c>
+      <c r="J85" t="s">
         <v>169</v>
-      </c>
-      <c r="J85" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="19"/>
       <c r="B86" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C86">
         <v>5</v>
@@ -3789,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F86">
         <v>4</v>
@@ -3801,16 +3792,16 @@
         <v>28</v>
       </c>
       <c r="I86" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J86" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="19"/>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="C87">
         <v>5</v>
@@ -3819,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -3831,16 +3822,19 @@
         <v>29</v>
       </c>
       <c r="I87" t="s">
+        <v>165</v>
+      </c>
+      <c r="J87" t="s">
         <v>166</v>
       </c>
-      <c r="J87" t="s">
-        <v>167</v>
+      <c r="K87" s="18" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="19"/>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="C88">
         <v>5</v>
@@ -3849,7 +3843,7 @@
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -3861,16 +3855,17 @@
         <v>30</v>
       </c>
       <c r="I88" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J88" t="s">
-        <v>168</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="K88" s="18"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="19"/>
       <c r="B89" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C89">
         <v>5</v>
@@ -3879,7 +3874,7 @@
         <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3891,17 +3886,15 @@
         <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J89" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="K89" s="16"/>
+    </row>
+    <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19"/>
-      <c r="B90" t="s">
-        <v>224</v>
-      </c>
       <c r="C90">
         <v>5</v>
       </c>
@@ -3909,7 +3902,7 @@
         <v>10</v>
       </c>
       <c r="E90" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F90">
         <v>3</v>
@@ -3920,15 +3913,10 @@
       <c r="H90">
         <v>32</v>
       </c>
-      <c r="K90" s="18" t="s">
-        <v>235</v>
-      </c>
+      <c r="K90" s="16"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="19"/>
-      <c r="B91" t="s">
-        <v>225</v>
-      </c>
       <c r="C91">
         <v>5</v>
       </c>
@@ -3936,7 +3924,7 @@
         <v>20</v>
       </c>
       <c r="E91" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F91">
         <v>4</v>
@@ -3947,23 +3935,23 @@
       <c r="H91">
         <v>33</v>
       </c>
-      <c r="K91" s="18"/>
+      <c r="K91" s="16"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C92">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3975,28 +3963,28 @@
         <v>34</v>
       </c>
       <c r="I92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J92" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="19"/>
       <c r="B93" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C93">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D93">
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -4008,26 +3996,26 @@
         <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J93" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K93" s="18"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="19"/>
       <c r="B94" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C94">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F94">
         <v>2</v>
@@ -4039,28 +4027,28 @@
         <v>36</v>
       </c>
       <c r="I94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J94" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K94" s="18" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="19"/>
       <c r="B95" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C95">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D95">
         <v>8</v>
       </c>
       <c r="E95" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F95">
         <v>3</v>
@@ -4072,26 +4060,26 @@
         <v>37</v>
       </c>
       <c r="I95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J95" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K95" s="18"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="19"/>
       <c r="B96" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C96">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D96">
         <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -4103,28 +4091,28 @@
         <v>38</v>
       </c>
       <c r="I96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J96" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K96" s="14" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="19"/>
       <c r="B97" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C97">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D97">
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -4136,28 +4124,28 @@
         <v>39</v>
       </c>
       <c r="I97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J97" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="19"/>
       <c r="B98" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C98">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D98">
         <v>40</v>
       </c>
       <c r="E98" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -4169,26 +4157,26 @@
         <v>40</v>
       </c>
       <c r="I98" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J98" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K98" s="16"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="19"/>
       <c r="B99" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C99">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D99">
         <v>80</v>
       </c>
       <c r="E99" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F99">
         <v>2</v>
@@ -4200,26 +4188,26 @@
         <v>41</v>
       </c>
       <c r="I99" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J99" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K99" s="16"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="19"/>
       <c r="B100" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C100">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -4231,25 +4219,25 @@
         <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J100" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="19"/>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C101">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D101">
         <v>2</v>
       </c>
       <c r="E101" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F101">
         <v>4</v>
@@ -4261,28 +4249,28 @@
         <v>43</v>
       </c>
       <c r="I101" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J101" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K101" s="14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="19"/>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C102">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D102">
         <v>4</v>
       </c>
       <c r="E102" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4294,28 +4282,28 @@
         <v>44</v>
       </c>
       <c r="I102" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J102" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K102" s="18" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="19"/>
       <c r="B103" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C103">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D103">
         <v>8</v>
       </c>
       <c r="E103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -4327,26 +4315,26 @@
         <v>45</v>
       </c>
       <c r="I103" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J103" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K103" s="18"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="19"/>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C104">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D104">
         <v>10</v>
       </c>
       <c r="E104" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F104">
         <v>2</v>
@@ -4358,28 +4346,28 @@
         <v>46</v>
       </c>
       <c r="I104" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K104" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="19"/>
       <c r="B105" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C105">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D105">
         <v>20</v>
       </c>
       <c r="E105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F105">
         <v>3</v>
@@ -4391,28 +4379,28 @@
         <v>47</v>
       </c>
       <c r="I105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K105" s="14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="19"/>
       <c r="B106" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C106">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D106">
         <v>40</v>
       </c>
       <c r="E106" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F106">
         <v>4</v>
@@ -4424,28 +4412,28 @@
         <v>48</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J106" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K106" s="14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="19"/>
       <c r="B107" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C107">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D107">
         <v>80</v>
       </c>
       <c r="E107" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -4457,28 +4445,28 @@
         <v>49</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J107" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K107" s="18" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="19"/>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C108">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -4490,26 +4478,23 @@
         <v>50</v>
       </c>
       <c r="I108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J108" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K108" s="18"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="19"/>
-      <c r="B109" t="s">
-        <v>255</v>
-      </c>
       <c r="C109">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F109">
         <v>2</v>
@@ -4521,10 +4506,10 @@
         <v>51</v>
       </c>
       <c r="I109" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J109" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -4533,13 +4518,13 @@
         <v>25</v>
       </c>
       <c r="C110">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D110">
         <v>4</v>
       </c>
       <c r="E110" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F110">
         <v>3</v>
@@ -4549,10 +4534,10 @@
       </c>
       <c r="H110" s="1"/>
       <c r="I110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J110" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -4561,13 +4546,13 @@
         <v>25</v>
       </c>
       <c r="C111">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D111">
         <v>8</v>
       </c>
       <c r="E111" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F111">
         <v>4</v>
@@ -4576,25 +4561,25 @@
         <v>4</v>
       </c>
       <c r="I111" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J111" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="19"/>
       <c r="B112" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C112">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D112">
         <v>10</v>
       </c>
       <c r="E112" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -4606,7 +4591,7 @@
         <v>52</v>
       </c>
       <c r="I112" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J112">
         <v>5</v>
@@ -4615,16 +4600,16 @@
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="19"/>
       <c r="B113" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C113">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D113">
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4636,7 +4621,7 @@
         <v>53</v>
       </c>
       <c r="I113" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J113">
         <v>4</v>
@@ -4645,16 +4630,16 @@
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="19"/>
       <c r="B114" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C114">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>40</v>
       </c>
       <c r="E114" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4666,7 +4651,7 @@
         <v>54</v>
       </c>
       <c r="I114" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J114">
         <v>3</v>
@@ -4678,13 +4663,13 @@
         <v>25</v>
       </c>
       <c r="C115">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D115">
         <v>80</v>
       </c>
       <c r="E115" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F115">
         <v>3</v>
@@ -4693,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="I115" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J115">
         <v>2</v>
@@ -4705,13 +4690,13 @@
         <v>25</v>
       </c>
       <c r="C116">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F116">
         <v>4</v>
@@ -4720,7 +4705,7 @@
         <v>4</v>
       </c>
       <c r="I116" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J116">
         <v>1</v>
@@ -4732,7 +4717,7 @@
         <v>25</v>
       </c>
       <c r="C117">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -4747,7 +4732,7 @@
         <v>25</v>
       </c>
       <c r="C118">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -4762,7 +4747,7 @@
         <v>25</v>
       </c>
       <c r="C119">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D119">
         <v>8</v>
@@ -4778,7 +4763,7 @@
         <v>25</v>
       </c>
       <c r="C120">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D120">
         <v>10</v>
@@ -4793,7 +4778,7 @@
         <v>25</v>
       </c>
       <c r="C121">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D121">
         <v>20</v>
@@ -4807,7 +4792,7 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -4877,16 +4862,16 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B132" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H132">
         <v>90</v>
       </c>
       <c r="I132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J132">
         <v>1</v>
@@ -4895,13 +4880,13 @@
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="19"/>
       <c r="B133" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H133">
         <v>91</v>
       </c>
       <c r="I133" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J133">
         <v>2</v>
@@ -4921,7 +4906,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B136" t="s">
         <v>25</v>
@@ -4970,24 +4955,24 @@
         <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D144" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D145" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -4995,13 +4980,13 @@
         <v>67</v>
       </c>
       <c r="B146" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D146" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -5009,15 +4994,15 @@
         <v>72</v>
       </c>
       <c r="D147" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B148" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>73</v>
@@ -5028,7 +5013,7 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>74</v>
@@ -5042,7 +5027,7 @@
         <v>68</v>
       </c>
       <c r="B150" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D150" t="s">
         <v>115</v>
@@ -5050,7 +5035,7 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D151" t="s">
         <v>116</v>
@@ -5095,6 +5080,7 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="K87:K88"/>
     <mergeCell ref="A128:A131"/>
     <mergeCell ref="A132:A135"/>
     <mergeCell ref="A136:A139"/>
@@ -5105,7 +5091,6 @@
     <mergeCell ref="A92:A121"/>
     <mergeCell ref="K92:K93"/>
     <mergeCell ref="K94:K95"/>
-    <mergeCell ref="K90:K91"/>
     <mergeCell ref="K102:K103"/>
     <mergeCell ref="K107:K108"/>
   </mergeCells>
@@ -5145,22 +5130,22 @@
         <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>86</v>
@@ -5180,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5207,7 +5192,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5236,7 +5221,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -5265,7 +5250,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -5294,7 +5279,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -5323,7 +5308,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -5352,7 +5337,7 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -5381,7 +5366,7 @@
         <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -5410,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -5439,7 +5424,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -5468,7 +5453,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -5497,7 +5482,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -5526,7 +5511,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -5555,7 +5540,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -5584,7 +5569,7 @@
         <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -5613,7 +5598,7 @@
         <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -5642,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -5671,7 +5656,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -5700,7 +5685,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -5729,7 +5714,7 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -5743,10 +5728,10 @@
         <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -5761,7 +5746,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -5775,10 +5760,10 @@
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -5793,7 +5778,7 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -5807,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5825,7 +5810,7 @@
         <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -5839,10 +5824,10 @@
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -5857,7 +5842,7 @@
         <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -5871,10 +5856,10 @@
         <v>23</v>
       </c>
       <c r="I25" t="s">
+        <v>168</v>
+      </c>
+      <c r="J25" t="s">
         <v>169</v>
-      </c>
-      <c r="J25" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -5889,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -5903,10 +5888,10 @@
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -5921,7 +5906,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -5935,10 +5920,10 @@
         <v>25</v>
       </c>
       <c r="I27" t="s">
+        <v>165</v>
+      </c>
+      <c r="J27" t="s">
         <v>166</v>
-      </c>
-      <c r="J27" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -5953,7 +5938,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -5967,10 +5952,10 @@
         <v>26</v>
       </c>
       <c r="I28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5985,7 +5970,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -5999,10 +5984,10 @@
         <v>27</v>
       </c>
       <c r="I29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6017,7 +6002,7 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F30">
         <v>3</v>
@@ -6039,7 +6024,7 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F31">
         <v>4</v>
@@ -6063,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -6075,10 +6060,10 @@
         <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -6093,7 +6078,7 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -6106,10 +6091,10 @@
         <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -6124,7 +6109,7 @@
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -6137,10 +6122,10 @@
         <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -6155,7 +6140,7 @@
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -6168,10 +6153,10 @@
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -6186,7 +6171,7 @@
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -6199,10 +6184,10 @@
         <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -6217,7 +6202,7 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -6230,17 +6215,17 @@
         <v>64</v>
       </c>
       <c r="I37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M37" s="12"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="20"/>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C38">
         <v>19</v>
@@ -6249,7 +6234,7 @@
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -6262,16 +6247,16 @@
         <v>65</v>
       </c>
       <c r="I38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="20"/>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C39">
         <v>19</v>
@@ -6280,7 +6265,7 @@
         <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -6293,10 +6278,10 @@
         <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -6308,7 +6293,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -6318,10 +6303,10 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -6333,7 +6318,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -6343,10 +6328,10 @@
         <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -6361,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -6374,10 +6359,10 @@
         <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K42" t="s">
         <v>97</v>
@@ -6396,7 +6381,7 @@
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -6410,10 +6395,10 @@
         <v>29</v>
       </c>
       <c r="I43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -6425,7 +6410,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -6435,10 +6420,10 @@
         <v>12</v>
       </c>
       <c r="I44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -6453,7 +6438,7 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -6467,10 +6452,10 @@
         <v>30</v>
       </c>
       <c r="I45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -6485,7 +6470,7 @@
         <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -6499,10 +6484,10 @@
         <v>31</v>
       </c>
       <c r="I46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -6514,7 +6499,7 @@
         <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -6524,10 +6509,10 @@
         <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M47" s="12"/>
     </row>
@@ -6543,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -6557,10 +6542,10 @@
         <v>32</v>
       </c>
       <c r="I48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -6575,7 +6560,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -6589,10 +6574,10 @@
         <v>33</v>
       </c>
       <c r="I49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -6607,7 +6592,7 @@
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -6621,10 +6606,10 @@
         <v>34</v>
       </c>
       <c r="I50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -6639,7 +6624,7 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F51">
         <v>4</v>
@@ -6653,10 +6638,10 @@
         <v>35</v>
       </c>
       <c r="I51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -6671,7 +6656,7 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -6684,7 +6669,7 @@
         <v>67</v>
       </c>
       <c r="I52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J52">
         <v>5</v>
@@ -6702,7 +6687,7 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -6715,7 +6700,7 @@
         <v>68</v>
       </c>
       <c r="I53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J53">
         <v>4</v>
@@ -6733,7 +6718,7 @@
         <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -6746,7 +6731,7 @@
         <v>69</v>
       </c>
       <c r="I54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J54">
         <v>3</v>
@@ -6765,7 +6750,7 @@
         <v>80</v>
       </c>
       <c r="E55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -6778,7 +6763,7 @@
         <v>70</v>
       </c>
       <c r="I55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -6796,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -6809,7 +6794,7 @@
         <v>71</v>
       </c>
       <c r="I56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -6904,7 +6889,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -6916,10 +6901,10 @@
         <v>36</v>
       </c>
       <c r="I62" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -6934,7 +6919,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -6948,10 +6933,10 @@
         <v>37</v>
       </c>
       <c r="I63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -6966,7 +6951,7 @@
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64">
         <v>2</v>
@@ -6979,10 +6964,10 @@
         <v>57</v>
       </c>
       <c r="I64" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -6997,7 +6982,7 @@
         <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -7010,10 +6995,10 @@
         <v>58</v>
       </c>
       <c r="I65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -7025,7 +7010,7 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F66">
         <v>4</v>
@@ -7035,10 +7020,10 @@
         <v>4</v>
       </c>
       <c r="I66" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -7053,7 +7038,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -7067,10 +7052,10 @@
         <v>38</v>
       </c>
       <c r="I67" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J67" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -7085,7 +7070,7 @@
         <v>40</v>
       </c>
       <c r="E68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -7099,10 +7084,10 @@
         <v>39</v>
       </c>
       <c r="I68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -7117,7 +7102,7 @@
         <v>80</v>
       </c>
       <c r="E69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F69">
         <v>2</v>
@@ -7131,10 +7116,10 @@
         <v>40</v>
       </c>
       <c r="I69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J69" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K69">
         <v>41</v>
@@ -7149,7 +7134,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -7159,10 +7144,10 @@
         <v>8</v>
       </c>
       <c r="I70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -7174,7 +7159,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F71">
         <v>4</v>
@@ -7184,10 +7169,10 @@
         <v>9</v>
       </c>
       <c r="I71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -7202,7 +7187,7 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -7215,10 +7200,10 @@
         <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -7233,7 +7218,7 @@
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -7247,10 +7232,10 @@
         <v>43</v>
       </c>
       <c r="I73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K73">
         <v>44</v>
@@ -7268,7 +7253,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -7281,10 +7266,10 @@
         <v>45</v>
       </c>
       <c r="I74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -7299,7 +7284,7 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -7313,10 +7298,10 @@
         <v>46</v>
       </c>
       <c r="I75" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -7328,7 +7313,7 @@
         <v>40</v>
       </c>
       <c r="E76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F76">
         <v>4</v>
@@ -7338,10 +7323,10 @@
         <v>14</v>
       </c>
       <c r="I76" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J76" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -7356,7 +7341,7 @@
         <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -7370,10 +7355,10 @@
         <v>47</v>
       </c>
       <c r="I77" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -7388,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -7402,10 +7387,10 @@
         <v>48</v>
       </c>
       <c r="I78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J78" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -7420,7 +7405,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F79">
         <v>2</v>
@@ -7434,10 +7419,10 @@
         <v>49</v>
       </c>
       <c r="I79" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -7452,7 +7437,7 @@
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -7466,10 +7451,10 @@
         <v>50</v>
       </c>
       <c r="I80" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -7484,7 +7469,7 @@
         <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F81">
         <v>4</v>
@@ -7498,10 +7483,10 @@
         <v>51</v>
       </c>
       <c r="I81" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J81" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -7516,7 +7501,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -7530,7 +7515,7 @@
         <v>52</v>
       </c>
       <c r="I82" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J82">
         <v>5</v>
@@ -7548,7 +7533,7 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -7562,7 +7547,7 @@
         <v>53</v>
       </c>
       <c r="I83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J83">
         <v>4</v>
@@ -7580,7 +7565,7 @@
         <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F84">
         <v>2</v>
@@ -7594,7 +7579,7 @@
         <v>54</v>
       </c>
       <c r="I84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J84">
         <v>3</v>
@@ -7612,7 +7597,7 @@
         <v>80</v>
       </c>
       <c r="E85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F85">
         <v>3</v>
@@ -7626,7 +7611,7 @@
         <v>55</v>
       </c>
       <c r="I85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J85">
         <v>2</v>
@@ -7644,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F86">
         <v>4</v>
@@ -7658,7 +7643,7 @@
         <v>56</v>
       </c>
       <c r="I86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -7741,7 +7726,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="I92" s="14"/>
     </row>
@@ -7756,7 +7741,7 @@
         <v>90</v>
       </c>
       <c r="I93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -7771,7 +7756,7 @@
         <v>91</v>
       </c>
       <c r="I94" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -7786,7 +7771,7 @@
         <v>92</v>
       </c>
       <c r="I95" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -7801,7 +7786,7 @@
         <v>93</v>
       </c>
       <c r="I96" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J96">
         <v>2</v>
@@ -7845,7 +7830,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B101" t="s">
         <v>25</v>
@@ -7881,7 +7866,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B105" t="s">
         <v>25</v>
@@ -8081,22 +8066,22 @@
         <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>86</v>
@@ -8116,7 +8101,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8143,7 +8128,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -8172,7 +8157,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -8201,7 +8186,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -8230,7 +8215,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -8259,7 +8244,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -8288,7 +8273,7 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -8317,7 +8302,7 @@
         <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -8346,7 +8331,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -8375,7 +8360,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -8404,7 +8389,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -8433,7 +8418,7 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -8462,7 +8447,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -8491,7 +8476,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -8520,7 +8505,7 @@
         <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -8549,7 +8534,7 @@
         <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -8578,7 +8563,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -8607,7 +8592,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -8636,7 +8621,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -8665,7 +8650,7 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -8694,7 +8679,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -8708,7 +8693,7 @@
         <v>43</v>
       </c>
       <c r="I22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -8726,7 +8711,7 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8740,7 +8725,7 @@
         <v>44</v>
       </c>
       <c r="I23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -8758,7 +8743,7 @@
         <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -8772,7 +8757,7 @@
         <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J24">
         <v>3</v>
@@ -8790,7 +8775,7 @@
         <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -8800,7 +8785,7 @@
         <v>23</v>
       </c>
       <c r="I25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -8818,7 +8803,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -8828,7 +8813,7 @@
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -8958,7 +8943,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -8985,7 +8970,7 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -9014,7 +8999,7 @@
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -9043,7 +9028,7 @@
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -9072,7 +9057,7 @@
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -9101,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -9130,7 +9115,7 @@
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -9159,7 +9144,7 @@
         <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -9188,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -9217,7 +9202,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -9246,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -9275,7 +9260,7 @@
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -9304,7 +9289,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -9333,7 +9318,7 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -9362,7 +9347,7 @@
         <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -9391,7 +9376,7 @@
         <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -9420,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -9449,7 +9434,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -9478,7 +9463,7 @@
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -9507,7 +9492,7 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F51">
         <v>4</v>
@@ -9536,7 +9521,7 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -9550,7 +9535,7 @@
         <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J52">
         <v>5</v>
@@ -9568,7 +9553,7 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -9582,7 +9567,7 @@
         <v>67</v>
       </c>
       <c r="I53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J53">
         <v>4</v>
@@ -9600,7 +9585,7 @@
         <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -9614,7 +9599,7 @@
         <v>68</v>
       </c>
       <c r="I54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J54">
         <v>3</v>
@@ -9632,7 +9617,7 @@
         <v>80</v>
       </c>
       <c r="E55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -9642,7 +9627,7 @@
         <v>23</v>
       </c>
       <c r="I55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -9660,7 +9645,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -9670,7 +9655,7 @@
         <v>24</v>
       </c>
       <c r="I56" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -9785,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -9812,7 +9797,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -9841,7 +9826,7 @@
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64">
         <v>2</v>
@@ -9870,7 +9855,7 @@
         <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -9899,7 +9884,7 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F66">
         <v>4</v>
@@ -9928,7 +9913,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -9957,7 +9942,7 @@
         <v>40</v>
       </c>
       <c r="E68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -9986,7 +9971,7 @@
         <v>80</v>
       </c>
       <c r="E69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F69">
         <v>2</v>
@@ -10015,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -10044,7 +10029,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F71">
         <v>4</v>
@@ -10073,7 +10058,7 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -10102,7 +10087,7 @@
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -10131,7 +10116,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -10160,7 +10145,7 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -10189,7 +10174,7 @@
         <v>40</v>
       </c>
       <c r="E76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F76">
         <v>4</v>
@@ -10218,7 +10203,7 @@
         <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -10247,7 +10232,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -10276,7 +10261,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F79">
         <v>2</v>
@@ -10305,7 +10290,7 @@
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -10334,7 +10319,7 @@
         <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F81">
         <v>4</v>
@@ -10363,7 +10348,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -10377,7 +10362,7 @@
         <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J82">
         <v>5</v>
@@ -10395,7 +10380,7 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -10409,7 +10394,7 @@
         <v>21</v>
       </c>
       <c r="I83" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J83">
         <v>4</v>
@@ -10427,7 +10412,7 @@
         <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F84">
         <v>2</v>
@@ -10441,7 +10426,7 @@
         <v>22</v>
       </c>
       <c r="I84" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J84">
         <v>3</v>
@@ -10459,7 +10444,7 @@
         <v>80</v>
       </c>
       <c r="E85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F85">
         <v>3</v>
@@ -10469,7 +10454,7 @@
         <v>23</v>
       </c>
       <c r="I85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J85">
         <v>2</v>
@@ -10487,7 +10472,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F86">
         <v>4</v>
@@ -10497,7 +10482,7 @@
         <v>24</v>
       </c>
       <c r="I86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -11009,13 +10994,13 @@
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
       <c r="J3" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
       <c r="M3" s="25"/>
       <c r="N3" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O3" s="25"/>
       <c r="P3" s="25"/>
@@ -11029,13 +11014,13 @@
       <c r="X3" s="25"/>
       <c r="Y3" s="25"/>
       <c r="Z3" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA3" s="25"/>
       <c r="AB3" s="25"/>
       <c r="AC3" s="25"/>
       <c r="AD3" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE3" s="25"/>
       <c r="AF3" s="25"/>
@@ -11051,42 +11036,42 @@
       <c r="AP3" s="7"/>
       <c r="AQ3" s="7"/>
       <c r="AR3" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AS3" s="27"/>
       <c r="AT3" s="27"/>
       <c r="AU3" s="27"/>
       <c r="AV3" s="28"/>
       <c r="AW3" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AX3" s="25"/>
       <c r="AY3" s="25"/>
       <c r="AZ3" s="25"/>
       <c r="BA3" s="25"/>
       <c r="BB3" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BC3" s="25"/>
       <c r="BD3" s="25"/>
       <c r="BE3" s="25"/>
       <c r="BF3" s="25"/>
       <c r="BG3" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BH3" s="25"/>
       <c r="BI3" s="25"/>
       <c r="BJ3" s="25"/>
       <c r="BK3" s="25"/>
       <c r="BL3" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BM3" s="25"/>
       <c r="BN3" s="25"/>
       <c r="BO3" s="25"/>
       <c r="BP3" s="25"/>
       <c r="BQ3" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BR3" s="25"/>
       <c r="BS3" s="25"/>
@@ -11594,13 +11579,13 @@
       <c r="G3" s="25"/>
       <c r="H3" s="25"/>
       <c r="I3" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J3" s="25"/>
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
       <c r="M3" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N3" s="25"/>
       <c r="O3" s="25"/>
@@ -11614,13 +11599,13 @@
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
       <c r="Y3" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z3" s="25"/>
       <c r="AA3" s="25"/>
       <c r="AB3" s="25"/>
       <c r="AC3" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AD3" s="25"/>
       <c r="AE3" s="25"/>
@@ -11636,42 +11621,42 @@
       <c r="AO3" s="7"/>
       <c r="AP3" s="7"/>
       <c r="AQ3" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AR3" s="27"/>
       <c r="AS3" s="27"/>
       <c r="AT3" s="27"/>
       <c r="AU3" s="28"/>
       <c r="AV3" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AW3" s="25"/>
       <c r="AX3" s="25"/>
       <c r="AY3" s="25"/>
       <c r="AZ3" s="25"/>
       <c r="BA3" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BB3" s="25"/>
       <c r="BC3" s="25"/>
       <c r="BD3" s="25"/>
       <c r="BE3" s="25"/>
       <c r="BF3" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BG3" s="25"/>
       <c r="BH3" s="25"/>
       <c r="BI3" s="25"/>
       <c r="BJ3" s="25"/>
       <c r="BK3" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BL3" s="25"/>
       <c r="BM3" s="25"/>
       <c r="BN3" s="25"/>
       <c r="BO3" s="25"/>
       <c r="BP3" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BQ3" s="25"/>
       <c r="BR3" s="25"/>
@@ -12047,16 +12032,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="BU1:CB1"/>
     <mergeCell ref="AQ3:AU3"/>
     <mergeCell ref="AV3:AZ3"/>
     <mergeCell ref="BA3:BE3"/>
     <mergeCell ref="BF3:BJ3"/>
     <mergeCell ref="BK3:BO3"/>
-    <mergeCell ref="BP3:BT3"/>
-    <mergeCell ref="AW1:BD1"/>
-    <mergeCell ref="BE1:BL1"/>
-    <mergeCell ref="BM1:BT1"/>
-    <mergeCell ref="BU1:CB1"/>
     <mergeCell ref="CC1:CJ1"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="I3:L3"/>
@@ -12069,6 +12050,10 @@
     <mergeCell ref="Y1:AF1"/>
     <mergeCell ref="AG1:AN1"/>
     <mergeCell ref="AO1:AV1"/>
+    <mergeCell ref="BP3:BT3"/>
+    <mergeCell ref="AW1:BD1"/>
+    <mergeCell ref="BE1:BL1"/>
+    <mergeCell ref="BM1:BT1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
